--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D154CA08-DA5F-3F45-A55B-FAB09907C3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C23C324-A934-A947-81C5-6D43A867EEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="34420" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="68800" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="280">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -1082,8 +1082,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1228,6 +1228,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1240,6 +1241,21 @@
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color theme="1"/>
@@ -1276,6 +1292,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1290,20 +1307,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1379,6 +1383,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1426,6 +1431,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1735,24 +1741,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="42" customWidth="1"/>
-    <col min="8" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="16" width="18" customWidth="1"/>
-    <col min="17" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="60.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="60.33203125" customWidth="1"/>
-    <col min="22" max="22" width="60.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="9" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="42" style="16" customWidth="1"/>
+    <col min="8" max="9" width="16" style="16" customWidth="1"/>
+    <col min="10" max="10" width="18" style="16" customWidth="1"/>
+    <col min="11" max="11" width="22" style="16" customWidth="1"/>
+    <col min="12" max="12" width="18" style="16" customWidth="1"/>
+    <col min="13" max="13" width="16" style="16" customWidth="1"/>
+    <col min="14" max="16" width="18" style="16" customWidth="1"/>
+    <col min="17" max="18" width="16" style="16" customWidth="1"/>
+    <col min="19" max="19" width="60.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="60.33203125" style="16" customWidth="1"/>
+    <col min="22" max="22" width="60.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="10.83203125" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="98" x14ac:dyDescent="0.2">
@@ -1976,7 +1983,7 @@
         <v>190</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D4" s="8">
         <v>33</v>
@@ -2452,7 +2459,7 @@
       <c r="S10" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="T10" s="7" t="s">
+      <c r="T10" s="13" t="s">
         <v>173</v>
       </c>
       <c r="U10" s="7" t="s">
@@ -2469,7 +2476,7 @@
       <c r="A11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="7" t="s">
         <v>229</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -2484,7 +2491,7 @@
       <c r="F11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="7" t="s">
         <v>227</v>
       </c>
       <c r="H11" s="9" t="s">
@@ -2493,7 +2500,7 @@
       <c r="I11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="7" t="s">
         <v>230</v>
       </c>
       <c r="K11" s="7" t="s">
@@ -2529,18 +2536,18 @@
       <c r="U11" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="V11" s="14" t="s">
+      <c r="V11" s="11" t="s">
         <v>167</v>
       </c>
       <c r="W11" s="7" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:23" ht="154" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
         <v>236</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -2552,10 +2559,10 @@
       <c r="E12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="7" t="s">
         <v>232</v>
       </c>
       <c r="H12" s="9" t="s">
@@ -2564,7 +2571,7 @@
       <c r="I12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="7" t="s">
         <v>234</v>
       </c>
       <c r="K12" s="7" t="s">
@@ -2600,21 +2607,23 @@
       <c r="U12" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="V12" s="14" t="s">
+      <c r="V12" s="12" t="s">
         <v>166</v>
       </c>
       <c r="W12" s="7" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="280" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="C13" s="7"/>
+      <c r="C13" s="7" t="s">
+        <v>188</v>
+      </c>
       <c r="D13" s="8">
         <v>4</v>
       </c>
@@ -2624,7 +2633,7 @@
       <c r="F13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="7" t="s">
         <v>239</v>
       </c>
       <c r="H13" s="9" t="s">
@@ -2669,15 +2678,15 @@
       <c r="U13" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="V13" s="14" t="s">
+      <c r="V13" s="12" t="s">
         <v>165</v>
       </c>
       <c r="W13" s="7" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:23" ht="306" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
         <v>244</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -2695,7 +2704,7 @@
       <c r="F14" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="7" t="s">
         <v>241</v>
       </c>
       <c r="H14" s="9" t="s">
@@ -2704,7 +2713,7 @@
       <c r="I14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="7" t="s">
         <v>196</v>
       </c>
       <c r="K14" s="7" t="s">
@@ -2740,18 +2749,18 @@
       <c r="U14" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="V14" s="14" t="s">
+      <c r="V14" s="12" t="s">
         <v>164</v>
       </c>
       <c r="W14" s="7" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="42" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="7" t="s">
         <v>246</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -2766,7 +2775,7 @@
       <c r="F15" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="7" t="s">
         <v>245</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -2775,7 +2784,7 @@
       <c r="I15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="7" t="s">
         <v>196</v>
       </c>
       <c r="K15" s="7" t="s">
@@ -2811,18 +2820,18 @@
       <c r="U15" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="V15" s="14" t="s">
+      <c r="V15" s="12" t="s">
         <v>163</v>
       </c>
       <c r="W15" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="98" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="7" t="s">
         <v>249</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -2837,7 +2846,7 @@
       <c r="F16" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="7" t="s">
         <v>248</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -2877,17 +2886,17 @@
       <c r="T16" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="U16" s="7" t="s">
+      <c r="U16" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="V16" s="14" t="s">
+      <c r="V16" s="12" t="s">
         <v>153</v>
       </c>
       <c r="W16" s="7" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>78</v>
       </c>
@@ -2931,16 +2940,16 @@
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
+      <c r="V17" s="12"/>
       <c r="W17" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="28" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="7"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8">
         <v>16</v>
@@ -2951,14 +2960,14 @@
       <c r="F18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="7"/>
+      <c r="G18" s="13"/>
       <c r="H18" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="J18" s="7"/>
+      <c r="J18" s="13"/>
       <c r="K18" s="7" t="s">
         <v>85</v>
       </c>
@@ -2980,13 +2989,13 @@
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
+      <c r="V18" s="14"/>
       <c r="W18" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B19" s="7"/>
@@ -3000,14 +3009,14 @@
       <c r="F19" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G19" s="7"/>
+      <c r="G19" s="13"/>
       <c r="H19" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J19" s="7"/>
+      <c r="J19" s="13"/>
       <c r="K19" s="7" t="s">
         <v>89</v>
       </c>
@@ -3029,16 +3038,16 @@
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
+      <c r="V19" s="14"/>
       <c r="W19" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
+    <row r="20" spans="1:23" ht="98" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="13" t="s">
         <v>259</v>
       </c>
       <c r="C20" s="7" t="s">
@@ -3050,10 +3059,10 @@
       <c r="E20" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="13" t="s">
         <v>255</v>
       </c>
       <c r="H20" s="9" t="s">
@@ -3062,7 +3071,7 @@
       <c r="I20" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="13" t="s">
         <v>253</v>
       </c>
       <c r="K20" s="7" t="s">
@@ -3098,18 +3107,18 @@
       <c r="U20" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="V20" s="7" t="s">
+      <c r="V20" s="14" t="s">
         <v>257</v>
       </c>
       <c r="W20" s="7" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A21" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="7"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="7"/>
       <c r="D21" s="8">
         <v>19</v>
@@ -3117,17 +3126,17 @@
       <c r="E21" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="7"/>
+      <c r="G21" s="13"/>
       <c r="H21" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="7"/>
+      <c r="J21" s="13"/>
       <c r="K21" s="7" t="s">
         <v>89</v>
       </c>
@@ -3149,12 +3158,12 @@
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
+      <c r="V21" s="14"/>
       <c r="W21" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>95</v>
       </c>
@@ -3169,7 +3178,7 @@
       <c r="F22" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G22" s="7"/>
+      <c r="G22" s="13"/>
       <c r="H22" s="9" t="s">
         <v>19</v>
       </c>
@@ -3198,13 +3207,13 @@
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
+      <c r="V22" s="14"/>
       <c r="W22" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A23" s="15" t="s">
         <v>98</v>
       </c>
       <c r="B23" s="7"/>
@@ -3218,14 +3227,14 @@
       <c r="F23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="7"/>
+      <c r="G23" s="13"/>
       <c r="H23" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="7"/>
+      <c r="J23" s="13"/>
       <c r="K23" s="7" t="s">
         <v>89</v>
       </c>
@@ -3247,16 +3256,16 @@
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
+      <c r="V23" s="14"/>
       <c r="W23" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="7"/>
+      <c r="B24" s="13"/>
       <c r="C24" s="7"/>
       <c r="D24" s="8">
         <v>37</v>
@@ -3267,14 +3276,14 @@
       <c r="F24" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="G24" s="7"/>
+      <c r="G24" s="13"/>
       <c r="H24" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J24" s="7"/>
+      <c r="J24" s="13"/>
       <c r="K24" s="7" t="s">
         <v>32</v>
       </c>
@@ -3296,16 +3305,16 @@
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
       <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
+      <c r="V24" s="14"/>
       <c r="W24" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="7"/>
+      <c r="B25" s="13"/>
       <c r="C25" s="7"/>
       <c r="D25" s="8">
         <v>38</v>
@@ -3316,7 +3325,7 @@
       <c r="F25" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="G25" s="7"/>
+      <c r="G25" s="13"/>
       <c r="H25" s="9" t="s">
         <v>10</v>
       </c>
@@ -3345,12 +3354,12 @@
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
+      <c r="V25" s="14"/>
       <c r="W25" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>143</v>
       </c>
@@ -3399,7 +3408,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>152</v>
       </c>
@@ -3448,7 +3457,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>128</v>
       </c>
@@ -3497,11 +3506,11 @@
         <v>260</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A29" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B29" s="7"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="7"/>
       <c r="D29" s="8">
         <v>34</v>
@@ -3509,17 +3518,17 @@
       <c r="E29" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="G29" s="7"/>
+      <c r="G29" s="13"/>
       <c r="H29" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J29" s="7"/>
+      <c r="J29" s="13"/>
       <c r="K29" s="7" t="s">
         <v>20</v>
       </c>
@@ -3546,7 +3555,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>134</v>
       </c>
@@ -3595,7 +3604,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>136</v>
       </c>
@@ -3644,7 +3653,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="42" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>100</v>
       </c>
@@ -3693,7 +3702,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>105</v>
       </c>
@@ -3742,7 +3751,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="28" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>108</v>
       </c>
@@ -3791,7 +3800,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
         <v>111</v>
       </c>
@@ -3840,7 +3849,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>114</v>
       </c>
@@ -3889,7 +3898,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>117</v>
       </c>
@@ -3938,7 +3947,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
         <v>120</v>
       </c>
@@ -3987,7 +3996,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>122</v>
       </c>
@@ -4036,7 +4045,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
         <v>125</v>
       </c>
@@ -4084,6 +4093,231 @@
       <c r="W40" s="7" t="s">
         <v>260</v>
       </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="7"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="7"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
+      <c r="U44" s="7"/>
+      <c r="V44" s="7"/>
+      <c r="W44" s="7"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="7"/>
+      <c r="U48" s="7"/>
+      <c r="V48" s="7"/>
+      <c r="W48" s="7"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="7"/>
+      <c r="T49" s="7"/>
+      <c r="U49" s="7"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C23C324-A934-A947-81C5-6D43A867EEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B609106C-D3FF-F643-9CF4-49EF36CFEA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="68800" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,10 +36,30 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={DBA8E842-1B69-4E44-955F-86A6656A5A38}</author>
+    <author>tc={2603CD78-4DA2-7245-9496-2BEE29538FD4}</author>
     <author>tc={D89771A4-99A8-0740-A054-82109EE9B8C1}</author>
   </authors>
   <commentList>
-    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{D89771A4-99A8-0740-A054-82109EE9B8C1}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{DBA8E842-1B69-4E44-955F-86A6656A5A38}">
+      <text>
+        <t xml:space="preserve">[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    La fuente de datos de esta variable es el tracker de GLOBARIS
+</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{2603CD78-4DA2-7245-9496-2BEE29538FD4}">
+      <text>
+        <t xml:space="preserve">[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    La fuente de datos de esta variable es el monitor del RIGI del MECON
+</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="2" shapeId="0" xr:uid="{D89771A4-99A8-0740-A054-82109EE9B8C1}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -53,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="280">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -580,9 +600,6 @@
     <t>Fuentes</t>
   </si>
   <si>
-    <t>Res. 559/2025; Globaris</t>
-  </si>
-  <si>
     <t>Licuefacción</t>
   </si>
   <si>
@@ -607,9 +624,6 @@
     <t>fecha_publicacion_bo</t>
   </si>
   <si>
-    <t>Res. 302/2025; Globaris</t>
-  </si>
-  <si>
     <t>Minerales de primera y segunda categoría del Código de Minería de la Nación (excluidos potasio y litio)</t>
   </si>
   <si>
@@ -628,9 +642,6 @@
     <t>desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
   </si>
   <si>
-    <t>Res. 1553/2025; Globaris</t>
-  </si>
-  <si>
     <t>instalación de una planta flotante de licuefacción de gas natural para obtener Gas Natural Licuado (GNL)</t>
   </si>
   <si>
@@ -649,21 +660,12 @@
     <t>extracción directa de litio, nanofiltración y pretratamiento de salmuera que posibilitarán la extracción de litio sin la necesidad de concentración previa en piletas de evaporación, lo que reducirá significativamente el impacto ambiental y la alteración del paisaje, a la vez que también permitirá reducir la generación de residuos y la necesidad de reactivos químicos en el proceso.</t>
   </si>
   <si>
-    <t>Res. 735/2025; Globaris</t>
-  </si>
-  <si>
     <t>30-69228382-8</t>
   </si>
   <si>
     <t>Desarrollo, extracción y procesamiento de minerales sulfurados de cobre con recuperación de oro como subproducto del yacimiento “San Jorge”, y contempla la construcción y operación de una mina a cielo abierto y una planta concentradora basada en técnicas de flotación convencional</t>
   </si>
   <si>
-    <t>Res. 801/2026; Globaris</t>
-  </si>
-  <si>
-    <t>Res. 6/2026; Globaris</t>
-  </si>
-  <si>
     <t>Oro y Plata</t>
   </si>
   <si>
@@ -676,9 +678,6 @@
     <t>exploración de las concesiones mineras Gualcamayo 1 y Gualcamayo 2 y la determinación de la factibilidad del yacimiento de reservas minerales de oro y plata denominado “Carbonatos Profundos”, y la construcción, puesta en marcha y operación de la planta de tratamiento de dichos minerales extraídos del Proyecto</t>
   </si>
   <si>
-    <t>Res. 676/2026, Globaris</t>
-  </si>
-  <si>
     <t>Ampliación del Tramo I del Gasoducto Perito Francisco Pascasio Moreno (GPM)</t>
   </si>
   <si>
@@ -703,9 +702,6 @@
     <t>Desde Tratayén, Neuquén, hasta Salliqueló, Buenos Aires</t>
   </si>
   <si>
-    <t>Res. 562/2026; Globaris</t>
-  </si>
-  <si>
     <t>30-67305977-1</t>
   </si>
   <si>
@@ -715,9 +711,6 @@
     <t>Salta; Catamarca</t>
   </si>
   <si>
-    <t>Res. 413/2026; Globaris</t>
-  </si>
-  <si>
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/340249/20260401</t>
   </si>
   <si>
@@ -739,18 +732,12 @@
     <t>33-71879284-9</t>
   </si>
   <si>
-    <t>Res. 1028/2025; Globaris</t>
-  </si>
-  <si>
     <t>construcción y puesta en operación de una nueva planta de aceros largos, que incluye tanto la acería como la laminadora continua en tándem, de menores emisiones de dióxido de carbono (CO2) respecto de las tecnologías tradicionales y bajo un modelo de producción de economía circular que permitirá reducir el consumo de recursos naturales y disminuir la huella ambiental a partir del uso de un noventa y nueve coma cinco por ciento (99,5%) de chatarra como materia prima</t>
   </si>
   <si>
     <t>actividades de industrialización y/o procesamiento del mineral de hierro, el acero y/o sus aleaciones, para la obtención de productos en formas primarias y/o productos elaborados</t>
   </si>
   <si>
-    <t>Res. 1842/2025; Globaris</t>
-  </si>
-  <si>
     <t>30-71891156-3</t>
   </si>
   <si>
@@ -766,9 +753,6 @@
     <t>construcción de una puerta de enlace multimodal y un punto estratégico de conexión en la Vía Navegable Troncal, también llamada “Hidrovía Paraguay – Paraná”, con el desarrollo de tres (3) unidades de gestión portuaria que buscarán optimizar las operaciones logísticas de carga, descarga, almacenamiento y despacho de distintos tipos de mercaderías, atendiendo a las necesidades de tráfico marítimo y terrestre de la zona </t>
   </si>
   <si>
-    <t>Res. 1254/2025; Globaris</t>
-  </si>
-  <si>
     <t xml:space="preserve"> instalación de un parque eólico de ciento ochenta (180) megavatios (180 MW) ubicado en la localidad de Olavarría, provincia de Buenos Aires, que también involucra la construcción de una nueva estación transformadora (ET) de treinta y tres a ciento treinta y dos kilovoltios (33/132 Kv) simple barra con dos transformadores de ciento veinte megavoltiamperios (120 MVA) y tres (3) campos, una línea de alta tensión (LAT) de ciento treinta y dos kilovoltios (132 Kv) de aproximadamente veinticinco kilómetros (25 km) de longitud que vinculará el parque eólico con la ET Olavarría -propiedad de TRANSBA SA-, y las obras de ampliación del sistema de transporte que incluirán la repotenciación de los capacitores series en la ET Olavarría y la ampliación de banco de capacitores shunt en la ET Ezeiza</t>
   </si>
   <si>
@@ -784,21 +768,12 @@
     <t>construcción de una nueva Planta de Adsorción Selectiva (SA 1B) y una nueva Planta de Carbonato (PC 1B); asimismo, incluye la perforación de pozos de salmuera adicionales, la instalación de estanques, tuberías, servicios públicos y la construcción de edificios auxiliares para apoyar la operación y administración de la nueva producción de carbonato de litio (cf., RE-2025-96020090-APN-SCEYM#MEC), como así también, la construcción de una nueva Planta Compresora de Gas Natural en la localidad de Olacapato, departamento de Los Andes, provincia de Salta, situada dentro del radio de doscientos kilómetros (200 km) del Proyecto, que permitirá ampliar la capacidad de transporte de los gasoductos “La Puna” y “Fénix”, instalaciones asociadas directamente al abastecimiento y transporte de gas natural para la nueva producción del proyecto “Expansión Fase 1B”.</t>
   </si>
   <si>
-    <t>Res. 431/2026; Globaris</t>
-  </si>
-  <si>
-    <t>Expansión Fase 1B Fenix </t>
-  </si>
-  <si>
     <t>30-71899846-4</t>
   </si>
   <si>
     <t>roducción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
   </si>
   <si>
-    <t>Res. 1271/2025; Globaris</t>
-  </si>
-  <si>
     <t>30-71765521-0</t>
   </si>
   <si>
@@ -808,9 +783,6 @@
     <t>Energio Solar</t>
   </si>
   <si>
-    <t>Res. 1/2025, Globaris</t>
-  </si>
-  <si>
     <t>Ampliación Caucharí Olaroz</t>
   </si>
   <si>
@@ -829,9 +801,6 @@
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342818/20260605</t>
   </si>
   <si>
-    <t>Res. 825/2026, Globaris</t>
-  </si>
-  <si>
     <t>Que conforme surge de la presentación, se trata de la ampliación de un proyecto preexistente denominado Cauchari Olaroz con una capacidad productiva instalada de cuarenta mil toneladas (40.000 t) por año de carbonato de litio equivalente (en adelante LCE).</t>
   </si>
   <si>
@@ -893,6 +862,57 @@
   </si>
   <si>
     <t>Justificacion_preexistencia_boletin_oficial</t>
+  </si>
+  <si>
+    <t>Empleos (directos e indirectos)</t>
+  </si>
+  <si>
+    <t>Res. 559/2025; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 302/2025; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 1553/2025; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 735/2025; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 801/2026; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 6/2026; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 676/2026, Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 562/2026; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 413/2026; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 1028/2025; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 1842/2025; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 1254/2025; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 431/2026; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 1271/2025; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 1/2025, Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Res. 825/2026, Globaris; MECON</t>
   </si>
 </sst>
 </file>
@@ -902,7 +922,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -973,6 +993,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1037,7 +1062,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1085,6 +1110,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1092,50 +1120,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Notas" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1264,6 +1249,25 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1506,6 +1510,49 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1521,36 +1568,38 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Lucas Sebastian Ordoñez" id="{CC6B0CDD-571C-5947-AB3B-0FE73E1F689E}" userId="S::01OR42856583@campus.economicas.uba.ar::7e5516ec-a921-4253-95aa-4b0e13b66244" providerId="AD"/>
   <person displayName="Lucas Sebastian Ordoñez" id="{2E8DF262-CB25-3049-80AF-0C6513AADFB8}" userId="S::01or42856583@campus.economicas.uba.ar::7e5516ec-a921-4253-95aa-4b0e13b66244" providerId="AD"/>
 </personList>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProyectosIntegrados" displayName="ProyectosIntegrados" ref="A1:W40" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
-  <tableColumns count="23">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="VPU" dataDxfId="25"/>
-    <tableColumn id="22" xr3:uid="{48F4E9CA-8EE4-9B46-B775-30029B62248E}" name="Descripción_del_proyecto" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{59A3C3BF-E3A1-3748-85BC-5ADA196D8039}" name="Proyecto de Exportación Estrategia a Largo plazo " dataDxfId="23"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id_proyecto" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="empresa" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="titular_proyecto" dataDxfId="20"/>
-    <tableColumn id="17" xr3:uid="{E1C7B229-46A1-4B4F-9ADD-A9E811939D67}" name="CUIT" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="sector" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="subsector" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{3AFF64F9-973D-4A41-865B-D4166A5841A1}" name="actividad_subsector_resolución_MECON" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="provincia" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="localidad_region" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Monto (mill. USD)" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Activos Computables (mill. USD)" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Estado administrativo" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="fecha_presentacion" dataDxfId="10"/>
-    <tableColumn id="21" xr3:uid="{D27A2121-7D63-544C-B031-C3DB1A1B8B6A}" name="fecha_adhesion_rigi" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="fecha_publicacion_bo" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="norma_aprobacion" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{B0966B39-0FA3-9146-96DB-BD345771FAC8}" name="Clasificacion_preexistencia_boletin_oficial" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{36F41A70-CDCD-0440-8E79-C4973DF4F4B3}" name="Justificacion_preexistencia_boletin_oficial" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{BC53B1FB-4807-D244-BE0E-F220BF050122}" name="link_norma" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{6C16FCDF-822E-B843-A888-4F4B69680144}" name="Fuentes" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProyectosIntegrados" displayName="ProyectosIntegrados" ref="A1:X40" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
+  <tableColumns count="24">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="VPU" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{48F4E9CA-8EE4-9B46-B775-30029B62248E}" name="Descripción_del_proyecto" dataDxfId="22"/>
+    <tableColumn id="19" xr3:uid="{59A3C3BF-E3A1-3748-85BC-5ADA196D8039}" name="Proyecto de Exportación Estrategia a Largo plazo " dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id_proyecto" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="empresa" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="titular_proyecto" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{E1C7B229-46A1-4B4F-9ADD-A9E811939D67}" name="CUIT" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="sector" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="subsector" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{3AFF64F9-973D-4A41-865B-D4166A5841A1}" name="actividad_subsector_resolución_MECON" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="provincia" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="localidad_region" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Monto (mill. USD)" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Activos Computables (mill. USD)" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Estado administrativo" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{00D6C894-3563-A741-A5B5-7FF8DB602F8A}" name="Empleos (directos e indirectos)" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="fecha_presentacion" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{D27A2121-7D63-544C-B031-C3DB1A1B8B6A}" name="fecha_adhesion_rigi" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="fecha_publicacion_bo" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="norma_aprobacion" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B0966B39-0FA3-9146-96DB-BD345771FAC8}" name="Clasificacion_preexistencia_boletin_oficial" dataDxfId="3"/>
+    <tableColumn id="23" xr3:uid="{36F41A70-CDCD-0440-8E79-C4973DF4F4B3}" name="Justificacion_preexistencia_boletin_oficial" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{BC53B1FB-4807-D244-BE0E-F220BF050122}" name="link_norma" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{6C16FCDF-822E-B843-A888-4F4B69680144}" name="Fuentes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1732,6 +1781,14 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E1" dT="2026-06-15T21:16:51.15" personId="{CC6B0CDD-571C-5947-AB3B-0FE73E1F689E}" id="{DBA8E842-1B69-4E44-955F-86A6656A5A38}">
+    <text xml:space="preserve">La fuente de datos de esta variable es el tracker de GLOBARIS
+</text>
+  </threadedComment>
+  <threadedComment ref="P1" dT="2026-06-15T21:15:54.67" personId="{CC6B0CDD-571C-5947-AB3B-0FE73E1F689E}" id="{2603CD78-4DA2-7245-9496-2BEE29538FD4}">
+    <text xml:space="preserve">La fuente de datos de esta variable es el monitor del RIGI del MECON
+</text>
+  </threadedComment>
   <threadedComment ref="M3" dT="2026-06-09T13:10:11.61" personId="{2E8DF262-CB25-3049-80AF-0C6513AADFB8}" id="{D89771A4-99A8-0740-A054-82109EE9B8C1}">
     <text xml:space="preserve">Que el solicitante declaró que el proyecto implicará una inversión total de entre dólares estadounidenses dos mil novecientos millones (USD 2.900.000.000) y dólares estadounidenses tres mil doscientos millones (USD 3.200.000.000). Se computa el promedio
 </text>
@@ -1741,12 +1798,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" style="16" customWidth="1"/>
-    <col min="3" max="3" width="9" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="42" style="16" customWidth="1"/>
     <col min="8" max="9" width="16" style="16" customWidth="1"/>
@@ -1754,20 +1811,20 @@
     <col min="11" max="11" width="22" style="16" customWidth="1"/>
     <col min="12" max="12" width="18" style="16" customWidth="1"/>
     <col min="13" max="13" width="16" style="16" customWidth="1"/>
-    <col min="14" max="16" width="18" style="16" customWidth="1"/>
-    <col min="17" max="18" width="16" style="16" customWidth="1"/>
-    <col min="19" max="19" width="60.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="60.33203125" style="16" customWidth="1"/>
-    <col min="22" max="22" width="60.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="10.83203125" style="16"/>
+    <col min="14" max="17" width="18" style="16" customWidth="1"/>
+    <col min="18" max="19" width="16" style="16" customWidth="1"/>
+    <col min="20" max="20" width="60.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="60.33203125" style="16" customWidth="1"/>
+    <col min="23" max="23" width="60.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="10.83203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="98" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="56" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>172</v>
@@ -1779,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>169</v>
@@ -1791,7 +1848,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>4</v>
@@ -1808,37 +1865,40 @@
       <c r="O1" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="6" t="s">
-        <v>278</v>
-      </c>
       <c r="U1" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="V1" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="W1" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="X1" s="7" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="56" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="56" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>173</v>
@@ -1850,7 +1910,7 @@
         <v>41</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>170</v>
@@ -1859,7 +1919,7 @@
         <v>168</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>171</v>
@@ -1879,37 +1939,40 @@
       <c r="O2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="7">
+        <v>836</v>
+      </c>
+      <c r="Q2" s="10">
         <v>45617</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="R2" s="10">
         <v>45775</v>
       </c>
-      <c r="R2" s="10">
+      <c r="S2" s="10">
         <v>45776</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="T2" s="7" t="s">
-        <v>188</v>
-      </c>
       <c r="U2" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="V2" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="W2" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="W2" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="84" x14ac:dyDescent="0.2">
+      <c r="X2" s="7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="84" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>173</v>
@@ -1924,16 +1987,16 @@
         <v>67</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>168</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>42</v>
@@ -1950,37 +2013,40 @@
       <c r="O3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="7">
+        <v>3108</v>
+      </c>
+      <c r="Q3" s="10">
         <v>45611</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="R3" s="10">
         <v>45722</v>
       </c>
-      <c r="R3" s="10">
+      <c r="S3" s="10">
         <v>45736</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="W3" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="X3" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="70" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="V3" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="70" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>190</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>173</v>
@@ -1995,7 +2061,7 @@
         <v>76</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>19</v>
@@ -2004,7 +2070,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
@@ -2021,37 +2087,40 @@
       <c r="O4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="7">
+        <v>7391</v>
+      </c>
+      <c r="Q4" s="10">
         <v>45849</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="R4" s="10">
         <v>45925</v>
       </c>
-      <c r="R4" s="10">
+      <c r="S4" s="10">
         <v>45943</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="T4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="T4" s="7" t="s">
-        <v>264</v>
-      </c>
       <c r="U4" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="V4" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="W4" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="W4" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="140" x14ac:dyDescent="0.2">
+      <c r="X4" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="140" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>173</v>
@@ -2066,7 +2135,7 @@
         <v>55</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>19</v>
@@ -2075,7 +2144,7 @@
         <v>56</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
@@ -2092,40 +2161,43 @@
       <c r="O5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="7">
+        <v>1985</v>
+      </c>
+      <c r="Q5" s="10">
         <v>45713</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="R5" s="10">
         <v>45796</v>
       </c>
-      <c r="R5" s="10">
+      <c r="S5" s="10">
         <v>45807</v>
       </c>
-      <c r="S5" s="7" t="s">
+      <c r="T5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="T5" s="7" t="s">
+      <c r="U5" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="U5" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="V5" s="12" t="s">
+      <c r="V5" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="W5" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="W5" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="98" x14ac:dyDescent="0.2">
+      <c r="X5" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="98" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D6" s="8">
         <v>9</v>
@@ -2137,7 +2209,7 @@
         <v>51</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>19</v>
@@ -2146,7 +2218,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>38</v>
@@ -2163,40 +2235,43 @@
       <c r="O6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="7">
+        <v>6300</v>
+      </c>
+      <c r="Q6" s="10">
         <v>45967</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="R6" s="10">
         <v>46155</v>
       </c>
-      <c r="R6" s="10">
+      <c r="S6" s="10">
         <v>46168</v>
       </c>
-      <c r="S6" s="7" t="s">
+      <c r="T6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="T6" s="7" t="s">
-        <v>188</v>
-      </c>
       <c r="U6" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="V6" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="W6" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="W6" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="112" x14ac:dyDescent="0.2">
+      <c r="X6" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="112" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D7" s="8">
         <v>3</v>
@@ -2208,16 +2283,16 @@
         <v>24</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>25</v>
@@ -2234,40 +2309,43 @@
       <c r="O7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="7">
+        <v>4500</v>
+      </c>
+      <c r="Q7" s="10">
         <v>45814</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="R7" s="10">
         <v>45988</v>
       </c>
-      <c r="R7" s="10">
+      <c r="S7" s="10">
         <v>46035</v>
       </c>
-      <c r="S7" s="7" t="s">
+      <c r="T7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="T7" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="U7" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="V7" s="12" t="s">
+      <c r="U7" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="V7" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="W7" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="W7" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="84" x14ac:dyDescent="0.2">
+      <c r="X7" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="84" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
@@ -2279,22 +2357,22 @@
         <v>9</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>168</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="M8" s="9">
         <v>550</v>
@@ -2305,40 +2383,43 @@
       <c r="O8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="7">
+        <v>7535</v>
+      </c>
+      <c r="Q8" s="10">
         <v>45957</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="R8" s="10">
         <v>46142</v>
       </c>
-      <c r="R8" s="10">
+      <c r="S8" s="10">
         <v>46154</v>
       </c>
-      <c r="S8" s="7" t="s">
+      <c r="T8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="T8" s="7" t="s">
+      <c r="U8" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="U8" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="V8" s="12" t="s">
+      <c r="V8" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="W8" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="W8" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="98" x14ac:dyDescent="0.2">
+      <c r="X8" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="98" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D9" s="8">
         <v>2</v>
@@ -2350,19 +2431,19 @@
         <v>18</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>21</v>
@@ -2376,40 +2457,43 @@
       <c r="O9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="7">
+        <v>2013</v>
+      </c>
+      <c r="Q9" s="10">
         <v>45981</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="R9" s="10">
         <v>46080</v>
       </c>
-      <c r="R9" s="10">
+      <c r="S9" s="10">
         <v>46149</v>
       </c>
-      <c r="S9" s="7" t="s">
+      <c r="T9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="T9" s="7" t="s">
-        <v>188</v>
-      </c>
       <c r="U9" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="V9" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="W9" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="W9" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="168" x14ac:dyDescent="0.2">
+      <c r="X9" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="168" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D10" s="8">
         <v>14</v>
@@ -2418,19 +2502,19 @@
         <v>69</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -2447,40 +2531,43 @@
       <c r="O10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="7">
+        <v>1048</v>
+      </c>
+      <c r="Q10" s="10">
         <v>45873</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="R10" s="10">
         <v>46050</v>
       </c>
-      <c r="R10" s="10">
+      <c r="S10" s="10">
         <v>46111</v>
       </c>
-      <c r="S10" s="7" t="s">
+      <c r="T10" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="T10" s="13" t="s">
+      <c r="U10" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="U10" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="V10" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="W10" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="168" x14ac:dyDescent="0.2">
+      <c r="V10" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="W10" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="X10" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="168" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D11" s="8">
         <v>8</v>
@@ -2492,7 +2579,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>47</v>
@@ -2501,7 +2588,7 @@
         <v>47</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>32</v>
@@ -2518,40 +2605,43 @@
       <c r="O11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="7">
+        <v>3800</v>
+      </c>
+      <c r="Q11" s="10">
         <v>45638</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="R11" s="10">
         <v>45807</v>
       </c>
-      <c r="R11" s="10">
+      <c r="S11" s="10">
         <v>45859</v>
       </c>
-      <c r="S11" s="7" t="s">
+      <c r="T11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="T11" s="7" t="s">
-        <v>188</v>
-      </c>
       <c r="U11" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="V11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="V11" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="W11" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="W11" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="154" x14ac:dyDescent="0.2">
+      <c r="X11" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="154" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D12" s="8">
         <v>12</v>
@@ -2563,7 +2653,7 @@
         <v>61</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>62</v>
@@ -2572,7 +2662,7 @@
         <v>63</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>64</v>
@@ -2589,40 +2679,43 @@
       <c r="O12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="7">
+        <v>9700</v>
+      </c>
+      <c r="Q12" s="10">
         <v>45757</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="R12" s="10">
         <v>45953</v>
       </c>
-      <c r="R12" s="10">
+      <c r="S12" s="10">
         <v>45980</v>
       </c>
-      <c r="S12" s="7" t="s">
+      <c r="T12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="T12" s="7" t="s">
-        <v>188</v>
-      </c>
       <c r="U12" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="V12" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="V12" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="W12" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="W12" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="280" x14ac:dyDescent="0.2">
+      <c r="X12" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="280" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D13" s="8">
         <v>4</v>
@@ -2634,7 +2727,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>10</v>
@@ -2660,40 +2753,43 @@
       <c r="O13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="7">
+        <v>165</v>
+      </c>
+      <c r="Q13" s="10">
         <v>45656</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="R13" s="10">
         <v>45863</v>
       </c>
-      <c r="R13" s="10">
+      <c r="S13" s="10">
         <v>45895</v>
       </c>
-      <c r="S13" s="7" t="s">
+      <c r="T13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="T13" s="7" t="s">
-        <v>188</v>
-      </c>
       <c r="U13" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="V13" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="W13" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="W13" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="306" x14ac:dyDescent="0.2">
+      <c r="X13" s="7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="306" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>244</v>
+        <v>199</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D14" s="8">
         <v>11</v>
@@ -2702,10 +2798,10 @@
         <v>54</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>19</v>
@@ -2714,7 +2810,7 @@
         <v>56</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>58</v>
@@ -2731,40 +2827,43 @@
       <c r="O14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="7">
+        <v>1273</v>
+      </c>
+      <c r="Q14" s="10">
         <v>45898</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="R14" s="10">
         <v>46106</v>
       </c>
-      <c r="R14" s="10">
+      <c r="S14" s="10">
         <v>46112</v>
       </c>
-      <c r="S14" s="7" t="s">
+      <c r="T14" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="T14" s="7" t="s">
+      <c r="U14" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="U14" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="V14" s="12" t="s">
+      <c r="V14" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="W14" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="W14" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="42" x14ac:dyDescent="0.2">
+      <c r="X14" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="56" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>71</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D15" s="8">
         <v>39</v>
@@ -2776,7 +2875,7 @@
         <v>73</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>19</v>
@@ -2785,7 +2884,7 @@
         <v>56</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>58</v>
@@ -2802,40 +2901,43 @@
       <c r="O15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="7">
+        <v>670</v>
+      </c>
+      <c r="Q15" s="10">
         <v>45594</v>
       </c>
-      <c r="Q15" s="10">
+      <c r="R15" s="10">
         <v>45855</v>
       </c>
-      <c r="R15" s="10">
+      <c r="S15" s="10">
         <v>45896</v>
       </c>
-      <c r="S15" s="7" t="s">
+      <c r="T15" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="T15" s="7" t="s">
-        <v>188</v>
-      </c>
       <c r="U15" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="V15" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="V15" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="W15" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="W15" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="98" x14ac:dyDescent="0.2">
+      <c r="X15" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="98" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D16" s="8">
         <v>5</v>
@@ -2847,13 +2949,13 @@
         <v>37</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
@@ -2871,32 +2973,35 @@
       <c r="O16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="7">
+        <v>384</v>
+      </c>
+      <c r="Q16" s="10">
         <v>45590</v>
       </c>
-      <c r="Q16" s="10">
+      <c r="R16" s="10">
         <v>45642</v>
       </c>
-      <c r="R16" s="10">
+      <c r="S16" s="10">
         <v>45664</v>
       </c>
-      <c r="S16" s="7" t="s">
+      <c r="T16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="T16" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="U16" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="V16" s="12" t="s">
+      <c r="U16" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="V16" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="W16" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="W16" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>78</v>
       </c>
@@ -2932,20 +3037,21 @@
       <c r="O17" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="7"/>
+      <c r="Q17" s="10">
         <v>45671</v>
       </c>
-      <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
-      <c r="S17" s="7"/>
+      <c r="S17" s="10"/>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+      <c r="V17" s="7"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="28" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>81</v>
       </c>
@@ -2981,20 +3087,21 @@
       <c r="O18" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="7"/>
+      <c r="Q18" s="10">
         <v>45874</v>
       </c>
-      <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
-      <c r="S18" s="7"/>
+      <c r="S18" s="10"/>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+      <c r="V18" s="7"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="28" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>86</v>
       </c>
@@ -3030,28 +3137,29 @@
       <c r="O19" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="7"/>
+      <c r="Q19" s="10">
         <v>45771</v>
       </c>
-      <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
-      <c r="S19" s="7"/>
+      <c r="S19" s="10"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="98" x14ac:dyDescent="0.2">
+      <c r="V19" s="7"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="98" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D20" s="8">
         <v>18</v>
@@ -3060,10 +3168,10 @@
         <v>90</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>19</v>
@@ -3072,7 +3180,7 @@
         <v>56</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>91</v>
@@ -3089,32 +3197,35 @@
       <c r="O20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P20" s="10">
+      <c r="P20" s="7">
+        <v>1787</v>
+      </c>
+      <c r="Q20" s="10">
         <v>45795</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="R20" s="10">
         <v>46151</v>
       </c>
-      <c r="R20" s="10">
+      <c r="S20" s="10">
         <v>46177</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>256</v>
-      </c>
       <c r="T20" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="U20" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="U20" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="V20" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="W20" s="7" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V20" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="W20" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="X20" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>92</v>
       </c>
@@ -3150,20 +3261,21 @@
       <c r="O21" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P21" s="10">
+      <c r="P21" s="7"/>
+      <c r="Q21" s="10">
         <v>45859</v>
       </c>
-      <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
-      <c r="S21" s="7"/>
+      <c r="S21" s="10"/>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V21" s="7"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>95</v>
       </c>
@@ -3199,20 +3311,21 @@
       <c r="O22" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="7"/>
+      <c r="Q22" s="10">
         <v>45887</v>
       </c>
-      <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
-      <c r="S22" s="7"/>
+      <c r="S22" s="10"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V22" s="7"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
         <v>98</v>
       </c>
@@ -3248,20 +3361,21 @@
       <c r="O23" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="7"/>
+      <c r="Q23" s="10">
         <v>46175</v>
       </c>
-      <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
-      <c r="S23" s="7"/>
+      <c r="S23" s="10"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V23" s="7"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>138</v>
       </c>
@@ -3297,20 +3411,21 @@
       <c r="O24" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P24" s="10">
+      <c r="P24" s="7"/>
+      <c r="Q24" s="10">
         <v>46136</v>
       </c>
-      <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
-      <c r="S24" s="7"/>
+      <c r="S24" s="10"/>
       <c r="T24" s="7"/>
       <c r="U24" s="7"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V24" s="7"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>140</v>
       </c>
@@ -3346,20 +3461,21 @@
       <c r="O25" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P25" s="10">
+      <c r="P25" s="7"/>
+      <c r="Q25" s="10">
         <v>45954</v>
       </c>
-      <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
-      <c r="S25" s="7"/>
+      <c r="S25" s="10"/>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V25" s="7"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>143</v>
       </c>
@@ -3395,20 +3511,21 @@
       <c r="O26" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P26" s="10">
+      <c r="P26" s="7"/>
+      <c r="Q26" s="10">
         <v>46111</v>
       </c>
-      <c r="Q26" s="10"/>
       <c r="R26" s="10"/>
-      <c r="S26" s="7"/>
+      <c r="S26" s="10"/>
       <c r="T26" s="7"/>
       <c r="U26" s="7"/>
       <c r="V26" s="7"/>
-      <c r="W26" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W26" s="7"/>
+      <c r="X26" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>152</v>
       </c>
@@ -3444,20 +3561,21 @@
       <c r="O27" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="7"/>
+      <c r="Q27" s="10">
         <v>46157</v>
       </c>
-      <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
-      <c r="S27" s="7"/>
+      <c r="S27" s="10"/>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
-      <c r="W27" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+      <c r="W27" s="7"/>
+      <c r="X27" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>128</v>
       </c>
@@ -3493,20 +3611,21 @@
       <c r="O28" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P28" s="10">
+      <c r="P28" s="7"/>
+      <c r="Q28" s="10">
         <v>46157</v>
       </c>
-      <c r="Q28" s="10"/>
       <c r="R28" s="10"/>
-      <c r="S28" s="7"/>
+      <c r="S28" s="10"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
       <c r="V28" s="7"/>
-      <c r="W28" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W28" s="7"/>
+      <c r="X28" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
         <v>130</v>
       </c>
@@ -3542,20 +3661,21 @@
       <c r="O29" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="7"/>
+      <c r="Q29" s="10">
         <v>45717</v>
       </c>
-      <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
-      <c r="S29" s="7"/>
+      <c r="S29" s="10"/>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
-      <c r="W29" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W29" s="7"/>
+      <c r="X29" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>134</v>
       </c>
@@ -3591,20 +3711,21 @@
       <c r="O30" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="7"/>
+      <c r="Q30" s="10">
         <v>46099</v>
       </c>
-      <c r="Q30" s="10"/>
       <c r="R30" s="10"/>
-      <c r="S30" s="7"/>
+      <c r="S30" s="10"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
       <c r="V30" s="7"/>
-      <c r="W30" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W30" s="7"/>
+      <c r="X30" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>136</v>
       </c>
@@ -3640,20 +3761,21 @@
       <c r="O31" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P31" s="10">
+      <c r="P31" s="7"/>
+      <c r="Q31" s="10">
         <v>45887</v>
       </c>
-      <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
-      <c r="S31" s="7"/>
+      <c r="S31" s="10"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
-      <c r="W31" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" ht="42" x14ac:dyDescent="0.2">
+      <c r="W31" s="7"/>
+      <c r="X31" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="42" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>100</v>
       </c>
@@ -3689,20 +3811,21 @@
       <c r="O32" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P32" s="10" t="s">
+      <c r="P32" s="7"/>
+      <c r="Q32" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="Q32" s="10"/>
       <c r="R32" s="10"/>
-      <c r="S32" s="7"/>
+      <c r="S32" s="10"/>
       <c r="T32" s="7"/>
       <c r="U32" s="7"/>
       <c r="V32" s="7"/>
-      <c r="W32" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W32" s="7"/>
+      <c r="X32" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>105</v>
       </c>
@@ -3738,20 +3861,21 @@
       <c r="O33" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P33" s="10">
+      <c r="P33" s="7"/>
+      <c r="Q33" s="10">
         <v>45805</v>
       </c>
-      <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
-      <c r="S33" s="7"/>
+      <c r="S33" s="10"/>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
-      <c r="W33" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+      <c r="W33" s="7"/>
+      <c r="X33" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="28" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>108</v>
       </c>
@@ -3787,20 +3911,21 @@
       <c r="O34" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P34" s="10">
+      <c r="P34" s="7"/>
+      <c r="Q34" s="10">
         <v>46118</v>
       </c>
-      <c r="Q34" s="10"/>
       <c r="R34" s="10"/>
-      <c r="S34" s="7"/>
+      <c r="S34" s="10"/>
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
       <c r="V34" s="7"/>
-      <c r="W34" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W34" s="7"/>
+      <c r="X34" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
         <v>111</v>
       </c>
@@ -3836,20 +3961,21 @@
       <c r="O35" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P35" s="10">
+      <c r="P35" s="7"/>
+      <c r="Q35" s="10">
         <v>46081</v>
       </c>
-      <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
-      <c r="S35" s="7"/>
+      <c r="S35" s="10"/>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
-      <c r="W35" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W35" s="7"/>
+      <c r="X35" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>114</v>
       </c>
@@ -3885,20 +4011,21 @@
       <c r="O36" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P36" s="10">
+      <c r="P36" s="7"/>
+      <c r="Q36" s="10">
         <v>45839</v>
       </c>
-      <c r="Q36" s="10"/>
       <c r="R36" s="10"/>
-      <c r="S36" s="7"/>
+      <c r="S36" s="10"/>
       <c r="T36" s="7"/>
       <c r="U36" s="7"/>
       <c r="V36" s="7"/>
-      <c r="W36" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W36" s="7"/>
+      <c r="X36" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>117</v>
       </c>
@@ -3934,20 +4061,21 @@
       <c r="O37" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P37" s="10">
+      <c r="P37" s="7"/>
+      <c r="Q37" s="10">
         <v>45595</v>
       </c>
-      <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
-      <c r="S37" s="7"/>
+      <c r="S37" s="10"/>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
-      <c r="W37" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W37" s="7"/>
+      <c r="X37" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
         <v>120</v>
       </c>
@@ -3983,20 +4111,21 @@
       <c r="O38" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P38" s="10">
+      <c r="P38" s="7"/>
+      <c r="Q38" s="10">
         <v>45758</v>
       </c>
-      <c r="Q38" s="10"/>
       <c r="R38" s="10"/>
-      <c r="S38" s="7"/>
+      <c r="S38" s="10"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
       <c r="V38" s="7"/>
-      <c r="W38" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W38" s="7"/>
+      <c r="X38" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>122</v>
       </c>
@@ -4032,20 +4161,21 @@
       <c r="O39" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P39" s="10" t="s">
+      <c r="P39" s="7"/>
+      <c r="Q39" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
-      <c r="S39" s="7"/>
+      <c r="S39" s="10"/>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
-      <c r="W39" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W39" s="7"/>
+      <c r="X39" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
         <v>125</v>
       </c>
@@ -4081,20 +4211,21 @@
       <c r="O40" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P40" s="10">
+      <c r="P40" s="7"/>
+      <c r="Q40" s="10">
         <v>46002</v>
       </c>
-      <c r="Q40" s="10"/>
       <c r="R40" s="10"/>
-      <c r="S40" s="7"/>
+      <c r="S40" s="10"/>
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
       <c r="V40" s="7"/>
-      <c r="W40" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W40" s="7"/>
+      <c r="X40" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -4110,16 +4241,17 @@
       <c r="M41" s="9"/>
       <c r="N41" s="9"/>
       <c r="O41" s="7"/>
-      <c r="P41" s="10"/>
+      <c r="P41" s="7"/>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
-      <c r="S41" s="7"/>
+      <c r="S41" s="10"/>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="7"/>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -4135,16 +4267,17 @@
       <c r="M42" s="9"/>
       <c r="N42" s="9"/>
       <c r="O42" s="7"/>
-      <c r="P42" s="10"/>
+      <c r="P42" s="7"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
-      <c r="S42" s="7"/>
+      <c r="S42" s="10"/>
       <c r="T42" s="7"/>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
       <c r="W42" s="7"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="7"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -4160,16 +4293,17 @@
       <c r="M43" s="9"/>
       <c r="N43" s="9"/>
       <c r="O43" s="7"/>
-      <c r="P43" s="10"/>
+      <c r="P43" s="7"/>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
-      <c r="S43" s="7"/>
+      <c r="S43" s="10"/>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="7"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -4185,16 +4319,17 @@
       <c r="M44" s="9"/>
       <c r="N44" s="9"/>
       <c r="O44" s="7"/>
-      <c r="P44" s="10"/>
+      <c r="P44" s="7"/>
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
-      <c r="S44" s="7"/>
+      <c r="S44" s="10"/>
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
       <c r="V44" s="7"/>
       <c r="W44" s="7"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="7"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -4210,16 +4345,17 @@
       <c r="M45" s="9"/>
       <c r="N45" s="9"/>
       <c r="O45" s="7"/>
-      <c r="P45" s="10"/>
+      <c r="P45" s="7"/>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
-      <c r="S45" s="7"/>
+      <c r="S45" s="10"/>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
       <c r="W45" s="7"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="7"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -4235,16 +4371,17 @@
       <c r="M46" s="9"/>
       <c r="N46" s="9"/>
       <c r="O46" s="7"/>
-      <c r="P46" s="10"/>
+      <c r="P46" s="7"/>
       <c r="Q46" s="10"/>
       <c r="R46" s="10"/>
-      <c r="S46" s="7"/>
+      <c r="S46" s="10"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
       <c r="V46" s="7"/>
       <c r="W46" s="7"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="7"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -4260,16 +4397,17 @@
       <c r="M47" s="9"/>
       <c r="N47" s="9"/>
       <c r="O47" s="7"/>
-      <c r="P47" s="10"/>
+      <c r="P47" s="7"/>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
-      <c r="S47" s="7"/>
+      <c r="S47" s="10"/>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="7"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -4285,16 +4423,17 @@
       <c r="M48" s="9"/>
       <c r="N48" s="9"/>
       <c r="O48" s="7"/>
-      <c r="P48" s="10"/>
+      <c r="P48" s="7"/>
       <c r="Q48" s="10"/>
       <c r="R48" s="10"/>
-      <c r="S48" s="7"/>
+      <c r="S48" s="10"/>
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
       <c r="W48" s="7"/>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="7"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -4310,37 +4449,40 @@
       <c r="M49" s="9"/>
       <c r="N49" s="9"/>
       <c r="O49" s="7"/>
-      <c r="P49" s="10"/>
+      <c r="P49" s="7"/>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
-      <c r="S49" s="7"/>
+      <c r="S49" s="10"/>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="7"/>
       <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="V16" r:id="rId1" xr:uid="{980A8705-7984-584F-AA67-D26C392ABC82}"/>
-    <hyperlink ref="V2" r:id="rId2" xr:uid="{9D626AFB-AED7-6E45-B753-789A1F6791C1}"/>
-    <hyperlink ref="V3" r:id="rId3" xr:uid="{C1F9917A-BBEE-3848-A846-5585A2FCCC16}"/>
-    <hyperlink ref="V4" r:id="rId4" xr:uid="{E61BB65B-5618-D842-B6B5-1D004A053D60}"/>
-    <hyperlink ref="V5" r:id="rId5" xr:uid="{030CB02F-3E38-AE45-AC1C-EE5651975CBA}"/>
-    <hyperlink ref="V6" r:id="rId6" xr:uid="{232A6A28-624D-CE40-BFCA-AD0E1FB7DF56}"/>
-    <hyperlink ref="V7" r:id="rId7" xr:uid="{C26CF64B-E057-8241-B386-6B0B94FD84CC}"/>
-    <hyperlink ref="V8" r:id="rId8" xr:uid="{FF6237C1-652C-1A4A-B04E-3FB26C32DBD5}"/>
-    <hyperlink ref="V9" r:id="rId9" xr:uid="{FE5C09BA-9D83-1C4D-A289-7D742AB36DC4}"/>
-    <hyperlink ref="V10" r:id="rId10" xr:uid="{28CFDF16-2940-5642-9869-C1E5F4C077CE}"/>
-    <hyperlink ref="V11" r:id="rId11" xr:uid="{C215718F-64A5-EA4F-8EA7-85C30B114214}"/>
-    <hyperlink ref="V12" r:id="rId12" xr:uid="{BE9CC28B-94CE-B24E-A74E-3D2ADB3217C6}"/>
-    <hyperlink ref="V13" r:id="rId13" xr:uid="{66457491-26B9-9F44-8331-CABFE31C9F72}"/>
-    <hyperlink ref="V14" r:id="rId14" xr:uid="{56EA8146-7375-2940-8CE7-621D3D82E155}"/>
-    <hyperlink ref="V15" r:id="rId15" xr:uid="{B991F48F-963A-5548-9E1D-97F06C683698}"/>
+    <hyperlink ref="W16" r:id="rId1" xr:uid="{980A8705-7984-584F-AA67-D26C392ABC82}"/>
+    <hyperlink ref="W2" r:id="rId2" xr:uid="{9D626AFB-AED7-6E45-B753-789A1F6791C1}"/>
+    <hyperlink ref="W3" r:id="rId3" xr:uid="{C1F9917A-BBEE-3848-A846-5585A2FCCC16}"/>
+    <hyperlink ref="W4" r:id="rId4" xr:uid="{E61BB65B-5618-D842-B6B5-1D004A053D60}"/>
+    <hyperlink ref="W5" r:id="rId5" xr:uid="{030CB02F-3E38-AE45-AC1C-EE5651975CBA}"/>
+    <hyperlink ref="W6" r:id="rId6" xr:uid="{232A6A28-624D-CE40-BFCA-AD0E1FB7DF56}"/>
+    <hyperlink ref="W7" r:id="rId7" xr:uid="{C26CF64B-E057-8241-B386-6B0B94FD84CC}"/>
+    <hyperlink ref="W8" r:id="rId8" xr:uid="{FF6237C1-652C-1A4A-B04E-3FB26C32DBD5}"/>
+    <hyperlink ref="W9" r:id="rId9" xr:uid="{FE5C09BA-9D83-1C4D-A289-7D742AB36DC4}"/>
+    <hyperlink ref="W10" r:id="rId10" xr:uid="{28CFDF16-2940-5642-9869-C1E5F4C077CE}"/>
+    <hyperlink ref="W11" r:id="rId11" xr:uid="{C215718F-64A5-EA4F-8EA7-85C30B114214}"/>
+    <hyperlink ref="W12" r:id="rId12" xr:uid="{BE9CC28B-94CE-B24E-A74E-3D2ADB3217C6}"/>
+    <hyperlink ref="W13" r:id="rId13" xr:uid="{66457491-26B9-9F44-8331-CABFE31C9F72}"/>
+    <hyperlink ref="W14" r:id="rId14" xr:uid="{56EA8146-7375-2940-8CE7-621D3D82E155}"/>
+    <hyperlink ref="W15" r:id="rId15" xr:uid="{B991F48F-963A-5548-9E1D-97F06C683698}"/>
+    <hyperlink ref="W20" r:id="rId16" xr:uid="{AE74A4E6-305E-5F49-B0FE-9AAB97F6A3DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
   <tableParts count="1">
-    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/rigi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35347B4-84B9-174A-807C-A26B3F1A4C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0051CB-3E0D-6D4C-8CAA-3236E3CFF468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="68800" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -585,9 +585,6 @@
     <t>Procesamiento, fraccionamiento, compresión y licuefacción</t>
   </si>
   <si>
-    <t xml:space="preserve">Proyecto de Exportación Estrategia a Largo plazo </t>
-  </si>
-  <si>
     <t>Sí</t>
   </si>
   <si>
@@ -976,6 +973,9 @@
   </si>
   <si>
     <t>Se identifican signos fuertes de preexistencia. El Proyecto Rincón de Aranda no surge con la resolución publicada el 21/07/2026. Antes de esa fecha existían antecedentes societarios, operativos, financieros y ambientales: Pampa Energía adquirió el control total del bloque en 2023; la etapa inicial del plan aprobado se declara iniciada el 08/07/2024; en 2024 ya existían EIAs y audiencias públicas para la CPF, oleoductos y gasoductos asociados; en 2025 la empresa ya informaba inversiones, solicitud RIGI, producción y pozos en operación. Por lo tanto, corresponde clasificarlo como proyecto preexistente al anuncio/aprobación oficial, aunque formalizado y ampliado bajo el RIGI como PEELP.</t>
+  </si>
+  <si>
+    <t>Proyectos de exportación estratégica de largo plazo (PEELP)</t>
   </si>
 </sst>
 </file>
@@ -1187,49 +1187,6 @@
     <cellStyle name="Notas" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="27">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1619,6 +1576,49 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1640,32 +1640,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProyectosIntegrados" displayName="ProyectosIntegrados" ref="A1:X40" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProyectosIntegrados" displayName="ProyectosIntegrados" ref="A1:X40" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
   <tableColumns count="24">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="VPU" dataDxfId="26"/>
-    <tableColumn id="22" xr3:uid="{48F4E9CA-8EE4-9B46-B775-30029B62248E}" name="Descripción_del_proyecto" dataDxfId="25"/>
-    <tableColumn id="19" xr3:uid="{59A3C3BF-E3A1-3748-85BC-5ADA196D8039}" name="Proyecto de Exportación Estrategia a Largo plazo " dataDxfId="24"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id_proyecto" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="empresa" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="titular_proyecto" dataDxfId="21"/>
-    <tableColumn id="17" xr3:uid="{E1C7B229-46A1-4B4F-9ADD-A9E811939D67}" name="CUIT" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="sector" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="subsector" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{3AFF64F9-973D-4A41-865B-D4166A5841A1}" name="actividad_subsector_resolución_MECON" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="provincia" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="localidad_region" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Monto (mill. USD)" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Activos Computables (mill. USD)" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Estado administrativo" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{00D6C894-3563-A741-A5B5-7FF8DB602F8A}" name="Empleos (directos e indirectos)" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="fecha_presentacion" dataDxfId="10"/>
-    <tableColumn id="21" xr3:uid="{D27A2121-7D63-544C-B031-C3DB1A1B8B6A}" name="fecha_adhesion_rigi" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="fecha_publicacion_bo" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="norma_aprobacion" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{B0966B39-0FA3-9146-96DB-BD345771FAC8}" name="Clasificacion_preexistencia_boletin_oficial" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{36F41A70-CDCD-0440-8E79-C4973DF4F4B3}" name="Justificacion_preexistencia_boletin_oficial" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{BC53B1FB-4807-D244-BE0E-F220BF050122}" name="link_norma" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{6C16FCDF-822E-B843-A888-4F4B69680144}" name="Fuentes" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="VPU" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{48F4E9CA-8EE4-9B46-B775-30029B62248E}" name="Descripción_del_proyecto" dataDxfId="22"/>
+    <tableColumn id="19" xr3:uid="{59A3C3BF-E3A1-3748-85BC-5ADA196D8039}" name="Proyectos de exportación estratégica de largo plazo (PEELP)" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id_proyecto" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="empresa" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="titular_proyecto" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{E1C7B229-46A1-4B4F-9ADD-A9E811939D67}" name="CUIT" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="sector" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="subsector" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{3AFF64F9-973D-4A41-865B-D4166A5841A1}" name="actividad_subsector_resolución_MECON" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="provincia" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="localidad_region" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Monto (mill. USD)" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Activos Computables (mill. USD)" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Estado administrativo" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{00D6C894-3563-A741-A5B5-7FF8DB602F8A}" name="Empleos (directos e indirectos)" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="fecha_presentacion" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{D27A2121-7D63-544C-B031-C3DB1A1B8B6A}" name="fecha_adhesion_rigi" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="fecha_publicacion_bo" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="norma_aprobacion" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B0966B39-0FA3-9146-96DB-BD345771FAC8}" name="Clasificacion_preexistencia_boletin_oficial" dataDxfId="3"/>
+    <tableColumn id="23" xr3:uid="{36F41A70-CDCD-0440-8E79-C4973DF4F4B3}" name="Justificacion_preexistencia_boletin_oficial" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{BC53B1FB-4807-D244-BE0E-F220BF050122}" name="link_norma" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{6C16FCDF-822E-B843-A888-4F4B69680144}" name="Fuentes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1870,15 +1870,15 @@
     <col min="1" max="16384" width="94.33203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="105" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>170</v>
+        <v>293</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>167</v>
@@ -1899,7 +1899,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>4</v>
@@ -1917,42 +1917,42 @@
         <v>149</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="R1" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>180</v>
       </c>
       <c r="T1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="U1" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="V1" s="6" t="s">
         <v>259</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="W1" s="7" t="s">
         <v>152</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" ht="60" x14ac:dyDescent="0.15">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="30" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D2" s="8">
         <v>7</v>
@@ -1961,7 +1961,7 @@
         <v>41</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>168</v>
@@ -1970,7 +1970,7 @@
         <v>166</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>169</v>
@@ -2006,27 +2006,27 @@
         <v>43</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V2" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W2" s="11" t="s">
         <v>154</v>
       </c>
       <c r="X2" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D3" s="8">
         <v>13</v>
@@ -2038,16 +2038,16 @@
         <v>67</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>166</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>42</v>
@@ -2080,27 +2080,27 @@
         <v>68</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W3" s="12" t="s">
         <v>153</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D4" s="8">
         <v>33</v>
@@ -2112,7 +2112,7 @@
         <v>76</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>19</v>
@@ -2121,7 +2121,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
@@ -2154,27 +2154,27 @@
         <v>77</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W4" s="12" t="s">
         <v>155</v>
       </c>
       <c r="X4" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="105" x14ac:dyDescent="0.15">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="60" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="8">
         <v>10</v>
@@ -2186,7 +2186,7 @@
         <v>55</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>19</v>
@@ -2195,7 +2195,7 @@
         <v>56</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
@@ -2228,27 +2228,27 @@
         <v>57</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="W5" s="12" t="s">
         <v>156</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D6" s="8">
         <v>9</v>
@@ -2260,7 +2260,7 @@
         <v>51</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>19</v>
@@ -2269,7 +2269,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>38</v>
@@ -2302,27 +2302,27 @@
         <v>53</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="W6" s="12" t="s">
         <v>157</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>198</v>
-      </c>
       <c r="C7" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D7" s="8">
         <v>3</v>
@@ -2334,16 +2334,16 @@
         <v>24</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>25</v>
@@ -2376,27 +2376,27 @@
         <v>27</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V7" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="W7" s="12" t="s">
         <v>158</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="75" x14ac:dyDescent="0.15">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
@@ -2408,22 +2408,22 @@
         <v>9</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>166</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K8" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>206</v>
       </c>
       <c r="M8" s="9">
         <v>550</v>
@@ -2450,27 +2450,27 @@
         <v>13</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="V8" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="W8" s="12" t="s">
         <v>159</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D9" s="8">
         <v>2</v>
@@ -2482,19 +2482,19 @@
         <v>18</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>21</v>
@@ -2524,27 +2524,27 @@
         <v>22</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="W9" s="15" t="s">
         <v>160</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" ht="135" x14ac:dyDescent="0.15">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="75" x14ac:dyDescent="0.15">
       <c r="A10" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D10" s="8">
         <v>14</v>
@@ -2553,19 +2553,19 @@
         <v>69</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -2598,27 +2598,27 @@
         <v>70</v>
       </c>
       <c r="U10" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="V10" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W10" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="X10" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" ht="150" x14ac:dyDescent="0.15">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="75" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" s="8">
         <v>8</v>
@@ -2630,7 +2630,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>47</v>
@@ -2639,7 +2639,7 @@
         <v>47</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>32</v>
@@ -2672,27 +2672,27 @@
         <v>48</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="W11" s="11" t="s">
         <v>165</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" ht="135" x14ac:dyDescent="0.15">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="60" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D12" s="8">
         <v>12</v>
@@ -2704,7 +2704,7 @@
         <v>61</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>62</v>
@@ -2713,7 +2713,7 @@
         <v>63</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>64</v>
@@ -2746,27 +2746,27 @@
         <v>65</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="W12" s="12" t="s">
         <v>164</v>
       </c>
       <c r="X12" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="240" x14ac:dyDescent="0.15">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="120" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D13" s="8">
         <v>4</v>
@@ -2778,7 +2778,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>10</v>
@@ -2820,27 +2820,27 @@
         <v>34</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="W13" s="12" t="s">
         <v>163</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="240" x14ac:dyDescent="0.15">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="120" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D14" s="8">
         <v>11</v>
@@ -2849,10 +2849,10 @@
         <v>54</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>226</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>227</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>19</v>
@@ -2861,7 +2861,7 @@
         <v>56</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>58</v>
@@ -2894,27 +2894,27 @@
         <v>59</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="W14" s="12" t="s">
         <v>162</v>
       </c>
       <c r="X14" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="60" x14ac:dyDescent="0.15">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>71</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D15" s="8">
         <v>39</v>
@@ -2926,7 +2926,7 @@
         <v>73</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>19</v>
@@ -2935,7 +2935,7 @@
         <v>56</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>58</v>
@@ -2968,27 +2968,27 @@
         <v>74</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="W15" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X15" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" ht="75" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D16" s="8">
         <v>5</v>
@@ -3000,13 +3000,13 @@
         <v>37</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
@@ -3040,19 +3040,19 @@
         <v>39</v>
       </c>
       <c r="U16" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V16" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="W16" s="12" t="s">
         <v>151</v>
       </c>
       <c r="X16" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="30" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
         <v>78</v>
       </c>
@@ -3099,10 +3099,10 @@
       <c r="V17" s="7"/>
       <c r="W17" s="12"/>
       <c r="X17" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" ht="30" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
         <v>81</v>
       </c>
@@ -3149,10 +3149,10 @@
       <c r="V18" s="7"/>
       <c r="W18" s="15"/>
       <c r="X18" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="30" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="14" t="s">
         <v>86</v>
       </c>
@@ -3199,18 +3199,18 @@
       <c r="V19" s="7"/>
       <c r="W19" s="15"/>
       <c r="X19" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" ht="75" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D20" s="8">
         <v>18</v>
@@ -3219,10 +3219,10 @@
         <v>90</v>
       </c>
       <c r="F20" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G20" s="14" t="s">
         <v>236</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>237</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>19</v>
@@ -3231,7 +3231,7 @@
         <v>56</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>91</v>
@@ -3261,19 +3261,19 @@
         <v>46177</v>
       </c>
       <c r="T20" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="V20" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="W20" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="U20" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="V20" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="W20" s="15" t="s">
-        <v>239</v>
-      </c>
       <c r="X20" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3323,7 +3323,7 @@
       <c r="V21" s="7"/>
       <c r="W21" s="15"/>
       <c r="X21" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3373,7 +3373,7 @@
       <c r="V22" s="7"/>
       <c r="W22" s="15"/>
       <c r="X22" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3423,7 +3423,7 @@
       <c r="V23" s="7"/>
       <c r="W23" s="15"/>
       <c r="X23" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3473,18 +3473,18 @@
       <c r="V24" s="7"/>
       <c r="W24" s="15"/>
       <c r="X24" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" ht="195" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="90" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>279</v>
-      </c>
       <c r="C25" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D25" s="8">
         <v>38</v>
@@ -3496,19 +3496,19 @@
         <v>140</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>166</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>12</v>
@@ -3535,19 +3535,19 @@
         <v>46198</v>
       </c>
       <c r="T25" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="U25" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="V25" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="W25" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="U25" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="V25" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="W25" s="12" t="s">
+      <c r="X25" s="7" t="s">
         <v>283</v>
-      </c>
-      <c r="X25" s="7" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3597,7 +3597,7 @@
       <c r="V26" s="7"/>
       <c r="W26" s="7"/>
       <c r="X26" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3647,10 +3647,10 @@
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" ht="30" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
         <v>127</v>
       </c>
@@ -3697,7 +3697,7 @@
       <c r="V28" s="7"/>
       <c r="W28" s="7"/>
       <c r="X28" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3747,10 +3747,10 @@
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" ht="30" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
         <v>133</v>
       </c>
@@ -3797,7 +3797,7 @@
       <c r="V30" s="7"/>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3847,10 +3847,10 @@
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
       <c r="X31" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
         <v>100</v>
       </c>
@@ -3897,7 +3897,7 @@
       <c r="V32" s="7"/>
       <c r="W32" s="7"/>
       <c r="X32" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3947,10 +3947,10 @@
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
       <c r="X33" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" ht="30" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
         <v>108</v>
       </c>
@@ -3997,7 +3997,7 @@
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
       <c r="X34" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -4047,18 +4047,18 @@
       <c r="V35" s="7"/>
       <c r="W35" s="7"/>
       <c r="X35" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" s="8">
         <v>26</v>
@@ -4070,7 +4070,7 @@
         <v>115</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>166</v>
@@ -4079,7 +4079,7 @@
         <v>166</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>89</v>
@@ -4109,19 +4109,19 @@
         <v>46224</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="V36" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="W36" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="X36" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -4171,7 +4171,7 @@
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -4221,7 +4221,7 @@
       <c r="V38" s="7"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -4271,7 +4271,7 @@
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -4321,7 +4321,7 @@
       <c r="V40" s="7"/>
       <c r="W40" s="7"/>
       <c r="X40" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.15">

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/rigi-dashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0051CB-3E0D-6D4C-8CAA-3236E3CFF468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56A6416-3343-BB45-8BF5-691227B47E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="68800" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36440" yWindow="0" windowWidth="32360" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="307">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -438,9 +438,6 @@
     <t>Sal de Vida S.A.</t>
   </si>
   <si>
-    <t>Salterra</t>
-  </si>
-  <si>
     <t>Zijin Mining (LieX S.A.) (China)</t>
   </si>
   <si>
@@ -630,15 +627,6 @@
     <t>Descripción_del_proyecto</t>
   </si>
   <si>
-    <t>desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
-  </si>
-  <si>
-    <t>instalación de una planta flotante de licuefacción de gas natural para obtener Gas Natural Licuado (GNL)</t>
-  </si>
-  <si>
-    <t>consiste en la construcción y desarrollo de un oleoducto, Iincrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
-  </si>
-  <si>
     <t>30-70708643-9</t>
   </si>
   <si>
@@ -648,9 +636,6 @@
     <t>Potasio y Litio</t>
   </si>
   <si>
-    <t>extracción directa de litio, nanofiltración y pretratamiento de salmuera que posibilitarán la extracción de litio sin la necesidad de concentración previa en piletas de evaporación, lo que reducirá significativamente el impacto ambiental y la alteración del paisaje, a la vez que también permitirá reducir la generación de residuos y la necesidad de reactivos químicos en el proceso.</t>
-  </si>
-  <si>
     <t>30-69228382-8</t>
   </si>
   <si>
@@ -666,9 +651,6 @@
     <t>Carbonatos Profundos (DCP)</t>
   </si>
   <si>
-    <t>exploración de las concesiones mineras Gualcamayo 1 y Gualcamayo 2 y la determinación de la factibilidad del yacimiento de reservas minerales de oro y plata denominado “Carbonatos Profundos”, y la construcción, puesta en marcha y operación de la planta de tratamiento de dichos minerales extraídos del Proyecto</t>
-  </si>
-  <si>
     <t>Ampliación del Tramo I del Gasoducto Perito Francisco Pascasio Moreno (GPM)</t>
   </si>
   <si>
@@ -684,9 +666,6 @@
     <t>VPU</t>
   </si>
   <si>
-    <t>construcción, financiamiento y Operación y Mantenimiento (O&amp;M) de la infraestructura involucrada para generar una capacidad incremental de catorce millones de metros cúbicos por día (14 MMm³/d) al Tramo I del Gasoducto Francisco Pascasio Moren</t>
-  </si>
-  <si>
     <t>Neuquén; Buenos Aires</t>
   </si>
   <si>
@@ -696,9 +675,6 @@
     <t>30-67305977-1</t>
   </si>
   <si>
-    <t>comprende actividades destinadas a la factibilidad, desarrollo, ejecución y operación del yacimiento de oro y plata “Diablillos”, integrado por quince (15) concesiones mineras contiguas y superpuestas en la zona limítrofe entre las provincias de Salta y Catamarca</t>
-  </si>
-  <si>
     <t>Salta; Catamarca</t>
   </si>
   <si>
@@ -723,9 +699,6 @@
     <t>33-71879284-9</t>
   </si>
   <si>
-    <t>construcción y puesta en operación de una nueva planta de aceros largos, que incluye tanto la acería como la laminadora continua en tándem, de menores emisiones de dióxido de carbono (CO2) respecto de las tecnologías tradicionales y bajo un modelo de producción de economía circular que permitirá reducir el consumo de recursos naturales y disminuir la huella ambiental a partir del uso de un noventa y nueve coma cinco por ciento (99,5%) de chatarra como materia prima</t>
-  </si>
-  <si>
     <t>actividades de industrialización y/o procesamiento del mineral de hierro, el acero y/o sus aleaciones, para la obtención de productos en formas primarias y/o productos elaborados</t>
   </si>
   <si>
@@ -741,12 +714,6 @@
     <t>actividad_subsector_resolución_MECON</t>
   </si>
   <si>
-    <t>construcción de una puerta de enlace multimodal y un punto estratégico de conexión en la Vía Navegable Troncal, también llamada “Hidrovía Paraguay – Paraná”, con el desarrollo de tres (3) unidades de gestión portuaria que buscarán optimizar las operaciones logísticas de carga, descarga, almacenamiento y despacho de distintos tipos de mercaderías, atendiendo a las necesidades de tráfico marítimo y terrestre de la zona </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> instalación de un parque eólico de ciento ochenta (180) megavatios (180 MW) ubicado en la localidad de Olavarría, provincia de Buenos Aires, que también involucra la construcción de una nueva estación transformadora (ET) de treinta y tres a ciento treinta y dos kilovoltios (33/132 Kv) simple barra con dos transformadores de ciento veinte megavoltiamperios (120 MVA) y tres (3) campos, una línea de alta tensión (LAT) de ciento treinta y dos kilovoltios (132 Kv) de aproximadamente veinticinco kilómetros (25 km) de longitud que vinculará el parque eólico con la ET Olavarría -propiedad de TRANSBA SA-, y las obras de ampliación del sistema de transporte que incluirán la repotenciación de los capacitores series en la ET Olavarría y la ampliación de banco de capacitores shunt en la ET Ezeiza</t>
-  </si>
-  <si>
     <t>30-71592816-3</t>
   </si>
   <si>
@@ -756,21 +723,12 @@
     <t>30-71906845-2</t>
   </si>
   <si>
-    <t>construcción de una nueva Planta de Adsorción Selectiva (SA 1B) y una nueva Planta de Carbonato (PC 1B); asimismo, incluye la perforación de pozos de salmuera adicionales, la instalación de estanques, tuberías, servicios públicos y la construcción de edificios auxiliares para apoyar la operación y administración de la nueva producción de carbonato de litio (cf., RE-2025-96020090-APN-SCEYM#MEC), como así también, la construcción de una nueva Planta Compresora de Gas Natural en la localidad de Olacapato, departamento de Los Andes, provincia de Salta, situada dentro del radio de doscientos kilómetros (200 km) del Proyecto, que permitirá ampliar la capacidad de transporte de los gasoductos “La Puna” y “Fénix”, instalaciones asociadas directamente al abastecimiento y transporte de gas natural para la nueva producción del proyecto “Expansión Fase 1B”.</t>
-  </si>
-  <si>
     <t>30-71899846-4</t>
   </si>
   <si>
-    <t>roducción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
-  </si>
-  <si>
     <t>30-71765521-0</t>
   </si>
   <si>
-    <t>parque solar fotovoltaico ubicado en la localidad de Jocolí del departamento Las Heras de la provincia de Mendoza, el cual tendrá una capacidad instalada por un total de trescientos cinco megavatios (305 MW) a desarrollarse en dos (2) etapas y proveerá energía</t>
-  </si>
-  <si>
     <t>Energio Solar</t>
   </si>
   <si>
@@ -907,9 +865,6 @@
   </si>
   <si>
     <t>Gasoducto dedicado para la Exportación de Gas Natural</t>
-  </si>
-  <si>
-    <t>construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
   </si>
   <si>
     <t> 30-71703621-9</t>
@@ -976,6 +931,90 @@
   </si>
   <si>
     <t>Proyectos de exportación estratégica de largo plazo (PEELP)</t>
+  </si>
+  <si>
+    <t>Res. 1153/2026; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345075/20260729</t>
+  </si>
+  <si>
+    <t>Res. 1153/2026</t>
+  </si>
+  <si>
+    <t>30-71929244-1</t>
+  </si>
+  <si>
+    <t>Proyecto de la Sucursal Dedicada de Liex S.A.</t>
+  </si>
+  <si>
+    <t>Se identifican signos muy fuertes de preexistencia. El proyecto aprobado bajo RIGI corresponde a LIEX S.A. Sucursal Dedicada en el Salar Tres Quebradas —3Q—, Catamarca. Aunque la Resolución 1153/2026 aprueba una inversión en activos computables por USD 594,136 millones para una planta de 40.000 t/año de carbonato de litio, el proyecto 3Q existía públicamente desde años previos: tuvo evaluación económica preliminar en 2017, estudio de factibilidad en 2021, acuerdo provincial ratificado por ley en 2022, adquisición por Zijin/LIEX en 2022, infraestructura eléctrica asociada tramitada desde 2023–2024 y primera fase en producción desde septiembre de 2025.</t>
+  </si>
+  <si>
+    <t>Construcción y operación de una planta de proceso y de la infraestructura asociada, diseñadas para alcanzar una capacidad de producción de cuarenta mil (40.000) toneladas anuales de carbonato de litio mediante el método de extracción directa</t>
+  </si>
+  <si>
+    <t>Instalación de una planta flotante de licuefacción de gas natural para obtener Gas Natural Licuado (GNL)</t>
+  </si>
+  <si>
+    <t>Consiste en la construcción y desarrollo de un oleoducto, Iincrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
+  </si>
+  <si>
+    <t>Desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
+  </si>
+  <si>
+    <t>Extracción directa de litio, nanofiltración y pretratamiento de salmuera que posibilitarán la extracción de litio sin la necesidad de concentración previa en piletas de evaporación, lo que reducirá significativamente el impacto ambiental y la alteración del paisaje, a la vez que también permitirá reducir la generación de residuos y la necesidad de reactivos químicos en el proceso.</t>
+  </si>
+  <si>
+    <t>Exploración de las concesiones mineras Gualcamayo 1 y Gualcamayo 2 y la determinación de la factibilidad del yacimiento de reservas minerales de oro y plata denominado “Carbonatos Profundos”, y la construcción, puesta en marcha y operación de la planta de tratamiento de dichos minerales extraídos del Proyecto</t>
+  </si>
+  <si>
+    <t>Construcción, financiamiento y Operación y Mantenimiento (O&amp;M) de la infraestructura involucrada para generar una capacidad incremental de catorce millones de metros cúbicos por día (14 MMm³/d) al Tramo I del Gasoducto Francisco Pascasio Moren</t>
+  </si>
+  <si>
+    <t>Comprende actividades destinadas a la factibilidad, desarrollo, ejecución y operación del yacimiento de oro y plata “Diablillos”, integrado por quince (15) concesiones mineras contiguas y superpuestas en la zona limítrofe entre las provincias de Salta y Catamarca</t>
+  </si>
+  <si>
+    <t>Construcción y puesta en operación de una nueva planta de aceros largos, que incluye tanto la acería como la laminadora continua en tándem, de menores emisiones de dióxido de carbono (CO2) respecto de las tecnologías tradicionales y bajo un modelo de producción de economía circular que permitirá reducir el consumo de recursos naturales y disminuir la huella ambiental a partir del uso de un noventa y nueve coma cinco por ciento (99,5%) de chatarra como materia prima</t>
+  </si>
+  <si>
+    <t>Construcción de una puerta de enlace multimodal y un punto estratégico de conexión en la Vía Navegable Troncal, también llamada “Hidrovía Paraguay – Paraná”, con el desarrollo de tres (3) unidades de gestión portuaria que buscarán optimizar las operaciones logísticas de carga, descarga, almacenamiento y despacho de distintos tipos de mercaderías, atendiendo a las necesidades de tráfico marítimo y terrestre de la zona </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Instalación de un parque eólico de ciento ochenta (180) megavatios (180 MW) ubicado en la localidad de Olavarría, provincia de Buenos Aires, que también involucra la construcción de una nueva estación transformadora (ET) de treinta y tres a ciento treinta y dos kilovoltios (33/132 Kv) simple barra con dos transformadores de ciento veinte megavoltiamperios (120 MVA) y tres (3) campos, una línea de alta tensión (LAT) de ciento treinta y dos kilovoltios (132 Kv) de aproximadamente veinticinco kilómetros (25 km) de longitud que vinculará el parque eólico con la ET Olavarría -propiedad de TRANSBA SA-, y las obras de ampliación del sistema de transporte que incluirán la repotenciación de los capacitores series en la ET Olavarría y la ampliación de banco de capacitores shunt en la ET Ezeiza</t>
+  </si>
+  <si>
+    <t>Construcción de una nueva Planta de Adsorción Selectiva (SA 1B) y una nueva Planta de Carbonato (PC 1B); asimismo, incluye la perforación de pozos de salmuera adicionales, la instalación de estanques, tuberías, servicios públicos y la construcción de edificios auxiliares para apoyar la operación y administración de la nueva producción de carbonato de litio (cf., RE-2025-96020090-APN-SCEYM#MEC), como así también, la construcción de una nueva Planta Compresora de Gas Natural en la localidad de Olacapato, departamento de Los Andes, provincia de Salta, situada dentro del radio de doscientos kilómetros (200 km) del Proyecto, que permitirá ampliar la capacidad de transporte de los gasoductos “La Puna” y “Fénix”, instalaciones asociadas directamente al abastecimiento y transporte de gas natural para la nueva producción del proyecto “Expansión Fase 1B”.</t>
+  </si>
+  <si>
+    <t>Producción de doce mil (12.000) toneladas anuales de carbonato de litio equivalente (LCE)</t>
+  </si>
+  <si>
+    <t>Parque solar fotovoltaico ubicado en la localidad de Jocolí del departamento Las Heras de la provincia de Mendoza, el cual tendrá una capacidad instalada por un total de trescientos cinco megavatios (305 MW) a desarrollarse en dos (2) etapas y proveerá energía</t>
+  </si>
+  <si>
+    <t>Construcción, operación y mantenimiento de un gasoducto dedicado de gas natural destinado exclusivamente a la exportación de Gas Natural Licuado (GNL) que se extenderá desde el Predio Cabecera Tratayén, en la provincia del Neuquén hasta la Estación Compresora San Antonio Oeste en el Golfo San Matías, sito en la provincia de Río Negro, de aproximadamente cuatrocientos ochenta kilómetros (480 km) de longitud, y treinta y seis pulgadas (36”) de diámetro, siendo el objetivo central evacuar la producción incremental de la cuenca Neuquina hacia terminales licuefactoras, aprovechando el potencial de recursos no convencionales provenientes de la formación Vaca Muerta</t>
+  </si>
+  <si>
+    <t>33-61913055-9</t>
+  </si>
+  <si>
+    <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución.</t>
+  </si>
+  <si>
+    <t>Cobre, Oro y Plata</t>
+  </si>
+  <si>
+    <t>Res. 1154/2026</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345167/20260730</t>
+  </si>
+  <si>
+    <t>Res. 1154/2026; Globaris; MECON</t>
+  </si>
+  <si>
+    <t>Antes del anuncio inicial del RIGI, Josemaría ya contaba con una factibilidad de noviembre de 2020, una evaluación ambiental aprobada en abril de 2022, ingeniería, adquisición de equipos de larga entrega y USD 276 millones de gastos de capital durante 2023; Filo del Sol también poseía prefactibilidades y exploración avanzada. Estos antecedentes corresponden a los mismos depósitos y, principalmente, a la actual primera etapa basada en Josemaría. Sin embargo, la sociedad conjunta BHP–Lundin se constituyó en enero de 2025, la primera evaluación técnica unificada apareció en febrero de 2026 y la decisión final de inversión continuaba pendiente después de la aprobación.</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1164,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1174,10 +1213,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1187,6 +1223,20 @@
     <cellStyle name="Notas" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="27">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1595,20 +1645,6 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
@@ -1640,32 +1676,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProyectosIntegrados" displayName="ProyectosIntegrados" ref="A1:X40" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProyectosIntegrados" displayName="ProyectosIntegrados" ref="A1:X40" headerRowDxfId="26" dataDxfId="0" totalsRowDxfId="25">
   <tableColumns count="24">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="VPU" dataDxfId="23"/>
-    <tableColumn id="22" xr3:uid="{48F4E9CA-8EE4-9B46-B775-30029B62248E}" name="Descripción_del_proyecto" dataDxfId="22"/>
-    <tableColumn id="19" xr3:uid="{59A3C3BF-E3A1-3748-85BC-5ADA196D8039}" name="Proyectos de exportación estratégica de largo plazo (PEELP)" dataDxfId="21"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id_proyecto" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="empresa" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="titular_proyecto" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{E1C7B229-46A1-4B4F-9ADD-A9E811939D67}" name="CUIT" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="sector" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="subsector" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{3AFF64F9-973D-4A41-865B-D4166A5841A1}" name="actividad_subsector_resolución_MECON" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="provincia" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="localidad_region" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Monto (mill. USD)" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Activos Computables (mill. USD)" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Estado administrativo" dataDxfId="9"/>
-    <tableColumn id="24" xr3:uid="{00D6C894-3563-A741-A5B5-7FF8DB602F8A}" name="Empleos (directos e indirectos)" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="fecha_presentacion" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{D27A2121-7D63-544C-B031-C3DB1A1B8B6A}" name="fecha_adhesion_rigi" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="fecha_publicacion_bo" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="norma_aprobacion" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{B0966B39-0FA3-9146-96DB-BD345771FAC8}" name="Clasificacion_preexistencia_boletin_oficial" dataDxfId="3"/>
-    <tableColumn id="23" xr3:uid="{36F41A70-CDCD-0440-8E79-C4973DF4F4B3}" name="Justificacion_preexistencia_boletin_oficial" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{BC53B1FB-4807-D244-BE0E-F220BF050122}" name="link_norma" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{6C16FCDF-822E-B843-A888-4F4B69680144}" name="Fuentes" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="VPU" dataDxfId="24"/>
+    <tableColumn id="22" xr3:uid="{48F4E9CA-8EE4-9B46-B775-30029B62248E}" name="Descripción_del_proyecto" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{59A3C3BF-E3A1-3748-85BC-5ADA196D8039}" name="Proyectos de exportación estratégica de largo plazo (PEELP)" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id_proyecto" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="empresa" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="titular_proyecto" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{E1C7B229-46A1-4B4F-9ADD-A9E811939D67}" name="CUIT" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="sector" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="subsector" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{3AFF64F9-973D-4A41-865B-D4166A5841A1}" name="actividad_subsector_resolución_MECON" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="provincia" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="localidad_region" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Monto (mill. USD)" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Activos Computables (mill. USD)" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Estado administrativo" dataDxfId="10"/>
+    <tableColumn id="24" xr3:uid="{00D6C894-3563-A741-A5B5-7FF8DB602F8A}" name="Empleos (directos e indirectos)" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="fecha_presentacion" dataDxfId="8"/>
+    <tableColumn id="21" xr3:uid="{D27A2121-7D63-544C-B031-C3DB1A1B8B6A}" name="fecha_adhesion_rigi" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="fecha_publicacion_bo" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="norma_aprobacion" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{B0966B39-0FA3-9146-96DB-BD345771FAC8}" name="Clasificacion_preexistencia_boletin_oficial" dataDxfId="4"/>
+    <tableColumn id="23" xr3:uid="{36F41A70-CDCD-0440-8E79-C4973DF4F4B3}" name="Justificacion_preexistencia_boletin_oficial" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{BC53B1FB-4807-D244-BE0E-F220BF050122}" name="link_norma" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{6C16FCDF-822E-B843-A888-4F4B69680144}" name="Fuentes" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1872,13 +1908,13 @@
   <sheetData>
     <row r="1" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1887,10 +1923,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>2</v>
@@ -1899,7 +1935,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>4</v>
@@ -1908,40 +1944,40 @@
         <v>5</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="P1" s="4" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="R1" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="T1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="30" x14ac:dyDescent="0.15">
@@ -1949,10 +1985,10 @@
         <v>40</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>186</v>
+        <v>286</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D2" s="8">
         <v>7</v>
@@ -1961,19 +1997,19 @@
         <v>41</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>168</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>169</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>42</v>
@@ -2006,27 +2042,27 @@
         <v>43</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V2" s="7" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="X2" s="7" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>187</v>
+        <v>287</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D3" s="8">
         <v>13</v>
@@ -2038,16 +2074,16 @@
         <v>67</v>
       </c>
       <c r="G3" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>174</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>175</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>42</v>
@@ -2080,27 +2116,27 @@
         <v>68</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>185</v>
+        <v>288</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D4" s="8">
         <v>33</v>
@@ -2112,7 +2148,7 @@
         <v>76</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>19</v>
@@ -2121,7 +2157,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
@@ -2154,27 +2190,27 @@
         <v>77</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="X4" s="7" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="60" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>191</v>
+        <v>289</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D5" s="8">
         <v>10</v>
@@ -2186,7 +2222,7 @@
         <v>55</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>19</v>
@@ -2195,7 +2231,7 @@
         <v>56</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
@@ -2228,16 +2264,16 @@
         <v>57</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="45" x14ac:dyDescent="0.15">
@@ -2245,10 +2281,10 @@
         <v>49</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D6" s="8">
         <v>9</v>
@@ -2260,7 +2296,7 @@
         <v>51</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>19</v>
@@ -2269,7 +2305,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>38</v>
@@ -2302,27 +2338,27 @@
         <v>53</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="W6" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>197</v>
+        <v>290</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D7" s="8">
         <v>3</v>
@@ -2334,16 +2370,16 @@
         <v>24</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>25</v>
@@ -2376,27 +2412,27 @@
         <v>27</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V7" s="13" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
@@ -2408,22 +2444,22 @@
         <v>9</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="M8" s="9">
         <v>550</v>
@@ -2450,16 +2486,16 @@
         <v>13</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V8" s="7" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="W8" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="45" x14ac:dyDescent="0.15">
@@ -2467,10 +2503,10 @@
         <v>16</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D9" s="8">
         <v>2</v>
@@ -2482,19 +2518,19 @@
         <v>18</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>21</v>
@@ -2524,27 +2560,27 @@
         <v>22</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="W9" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="75" x14ac:dyDescent="0.15">
       <c r="A10" s="14" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D10" s="8">
         <v>14</v>
@@ -2553,19 +2589,19 @@
         <v>69</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -2598,16 +2634,16 @@
         <v>70</v>
       </c>
       <c r="U10" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V10" s="7" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="W10" s="15" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="X10" s="7" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="75" x14ac:dyDescent="0.15">
@@ -2615,10 +2651,10 @@
         <v>44</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>216</v>
+        <v>293</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" s="8">
         <v>8</v>
@@ -2630,7 +2666,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>47</v>
@@ -2639,7 +2675,7 @@
         <v>47</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>32</v>
@@ -2672,27 +2708,27 @@
         <v>48</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="60" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>222</v>
+        <v>294</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" s="8">
         <v>12</v>
@@ -2704,7 +2740,7 @@
         <v>61</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>62</v>
@@ -2713,7 +2749,7 @@
         <v>63</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>64</v>
@@ -2746,16 +2782,16 @@
         <v>65</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X12" s="7" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="120" x14ac:dyDescent="0.15">
@@ -2763,10 +2799,10 @@
         <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>223</v>
+        <v>295</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D13" s="8">
         <v>4</v>
@@ -2778,7 +2814,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>10</v>
@@ -2820,27 +2856,27 @@
         <v>34</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="120" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D14" s="8">
         <v>11</v>
@@ -2849,10 +2885,10 @@
         <v>54</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>19</v>
@@ -2861,7 +2897,7 @@
         <v>56</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>58</v>
@@ -2894,16 +2930,16 @@
         <v>59</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="W14" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X14" s="7" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="45" x14ac:dyDescent="0.15">
@@ -2911,10 +2947,10 @@
         <v>71</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>229</v>
+        <v>297</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D15" s="8">
         <v>39</v>
@@ -2926,7 +2962,7 @@
         <v>73</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>19</v>
@@ -2935,7 +2971,7 @@
         <v>56</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>58</v>
@@ -2968,16 +3004,16 @@
         <v>74</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="W15" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X15" s="7" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="45" x14ac:dyDescent="0.15">
@@ -2985,10 +3021,10 @@
         <v>35</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>231</v>
+        <v>298</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D16" s="8">
         <v>5</v>
@@ -3000,13 +3036,13 @@
         <v>37</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
@@ -3040,16 +3076,16 @@
         <v>39</v>
       </c>
       <c r="U16" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V16" s="13" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="W16" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X16" s="7" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3086,7 +3122,7 @@
       </c>
       <c r="N17" s="9"/>
       <c r="O17" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="10">
@@ -3099,7 +3135,7 @@
       <c r="V17" s="7"/>
       <c r="W17" s="12"/>
       <c r="X17" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3136,7 +3172,7 @@
       </c>
       <c r="N18" s="9"/>
       <c r="O18" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P18" s="7"/>
       <c r="Q18" s="10">
@@ -3149,7 +3185,7 @@
       <c r="V18" s="7"/>
       <c r="W18" s="15"/>
       <c r="X18" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3186,7 +3222,7 @@
       </c>
       <c r="N19" s="9"/>
       <c r="O19" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="10">
@@ -3199,18 +3235,18 @@
       <c r="V19" s="7"/>
       <c r="W19" s="15"/>
       <c r="X19" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="45" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D20" s="8">
         <v>18</v>
@@ -3219,10 +3255,10 @@
         <v>90</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>19</v>
@@ -3231,7 +3267,7 @@
         <v>56</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>91</v>
@@ -3261,19 +3297,19 @@
         <v>46177</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V20" s="7" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="W20" s="15" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="X20" s="7" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3310,7 +3346,7 @@
       </c>
       <c r="N21" s="9"/>
       <c r="O21" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="10">
@@ -3323,7 +3359,7 @@
       <c r="V21" s="7"/>
       <c r="W21" s="15"/>
       <c r="X21" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3360,7 +3396,7 @@
       </c>
       <c r="N22" s="9"/>
       <c r="O22" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="10">
@@ -3373,7 +3409,7 @@
       <c r="V22" s="7"/>
       <c r="W22" s="15"/>
       <c r="X22" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3410,7 +3446,7 @@
       </c>
       <c r="N23" s="9"/>
       <c r="O23" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="10">
@@ -3423,12 +3459,12 @@
       <c r="V23" s="7"/>
       <c r="W23" s="15"/>
       <c r="X23" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="7"/>
@@ -3439,7 +3475,7 @@
         <v>114</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="9" t="s">
@@ -3460,7 +3496,7 @@
       </c>
       <c r="N24" s="9"/>
       <c r="O24" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P24" s="7"/>
       <c r="Q24" s="10">
@@ -3473,42 +3509,42 @@
       <c r="V24" s="7"/>
       <c r="W24" s="15"/>
       <c r="X24" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="90" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D25" s="8">
         <v>38</v>
       </c>
       <c r="E25" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>140</v>
-      </c>
       <c r="G25" s="7" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>12</v>
@@ -3535,24 +3571,24 @@
         <v>46198</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="W25" s="12" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -3560,10 +3596,10 @@
         <v>40</v>
       </c>
       <c r="E26" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>143</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="9" t="s">
@@ -3584,7 +3620,7 @@
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P26" s="7"/>
       <c r="Q26" s="10">
@@ -3597,12 +3633,12 @@
       <c r="V26" s="7"/>
       <c r="W26" s="7"/>
       <c r="X26" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -3610,7 +3646,7 @@
         <v>41</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>14</v>
@@ -3634,7 +3670,7 @@
       </c>
       <c r="N27" s="9"/>
       <c r="O27" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P27" s="7"/>
       <c r="Q27" s="10">
@@ -3647,12 +3683,12 @@
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -3660,7 +3696,7 @@
         <v>32</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>14</v>
@@ -3684,7 +3720,7 @@
       </c>
       <c r="N28" s="9"/>
       <c r="O28" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P28" s="7"/>
       <c r="Q28" s="10">
@@ -3697,12 +3733,12 @@
       <c r="V28" s="7"/>
       <c r="W28" s="7"/>
       <c r="X28" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="7"/>
@@ -3710,10 +3746,10 @@
         <v>34</v>
       </c>
       <c r="E29" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>130</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>131</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="9" t="s">
@@ -3734,7 +3770,7 @@
       </c>
       <c r="N29" s="9"/>
       <c r="O29" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="10">
@@ -3747,12 +3783,12 @@
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -3760,10 +3796,10 @@
         <v>35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="9" t="s">
@@ -3784,7 +3820,7 @@
       </c>
       <c r="N30" s="9"/>
       <c r="O30" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P30" s="7"/>
       <c r="Q30" s="10">
@@ -3797,12 +3833,12 @@
       <c r="V30" s="7"/>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -3813,7 +3849,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="9" t="s">
@@ -3834,7 +3870,7 @@
       </c>
       <c r="N31" s="9"/>
       <c r="O31" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="10">
@@ -3847,7 +3883,7 @@
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
       <c r="X31" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3884,7 +3920,7 @@
       </c>
       <c r="N32" s="9"/>
       <c r="O32" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P32" s="7"/>
       <c r="Q32" s="10" t="s">
@@ -3897,7 +3933,7 @@
       <c r="V32" s="7"/>
       <c r="W32" s="7"/>
       <c r="X32" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3934,7 +3970,7 @@
       </c>
       <c r="N33" s="9"/>
       <c r="O33" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="10">
@@ -3947,7 +3983,7 @@
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
       <c r="X33" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -3984,7 +4020,7 @@
       </c>
       <c r="N34" s="9"/>
       <c r="O34" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P34" s="7"/>
       <c r="Q34" s="10">
@@ -3997,7 +4033,7 @@
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
       <c r="X34" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -4034,7 +4070,7 @@
       </c>
       <c r="N35" s="9"/>
       <c r="O35" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P35" s="7"/>
       <c r="Q35" s="10">
@@ -4047,18 +4083,18 @@
       <c r="V35" s="7"/>
       <c r="W35" s="7"/>
       <c r="X35" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="90" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D36" s="8">
         <v>26</v>
@@ -4070,16 +4106,16 @@
         <v>115</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>89</v>
@@ -4109,19 +4145,19 @@
         <v>46224</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="V36" s="18" t="s">
-        <v>292</v>
+        <v>169</v>
+      </c>
+      <c r="V36" s="16" t="s">
+        <v>277</v>
       </c>
       <c r="W36" s="7" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="X36" s="7" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -4158,7 +4194,7 @@
       </c>
       <c r="N37" s="9"/>
       <c r="O37" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="10">
@@ -4171,7 +4207,7 @@
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="15" x14ac:dyDescent="0.15">
@@ -4208,7 +4244,7 @@
       </c>
       <c r="N38" s="9"/>
       <c r="O38" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P38" s="7"/>
       <c r="Q38" s="10">
@@ -4221,32 +4257,38 @@
       <c r="V38" s="7"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" ht="15" x14ac:dyDescent="0.15">
-      <c r="A39" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="7"/>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+      <c r="A39" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>285</v>
+      </c>
       <c r="C39" s="7"/>
       <c r="D39" s="8">
         <v>29</v>
       </c>
       <c r="E39" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="F39" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G39" s="7"/>
+      <c r="G39" s="17" t="s">
+        <v>282</v>
+      </c>
       <c r="H39" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J39" s="7"/>
+      <c r="J39" s="7" t="s">
+        <v>186</v>
+      </c>
       <c r="K39" s="7" t="s">
         <v>58</v>
       </c>
@@ -4256,47 +4298,71 @@
       <c r="M39" s="9">
         <v>710</v>
       </c>
-      <c r="N39" s="9"/>
+      <c r="N39" s="9">
+        <v>594.13599999999997</v>
+      </c>
       <c r="O39" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="7"/>
-      <c r="V39" s="7"/>
-      <c r="W39" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="P39" s="7">
+        <v>4406</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>46063</v>
+      </c>
+      <c r="R39" s="10">
+        <v>46206</v>
+      </c>
+      <c r="S39" s="10">
+        <v>46232</v>
+      </c>
+      <c r="T39" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="V39" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="W39" s="7" t="s">
+        <v>280</v>
+      </c>
       <c r="X39" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" ht="15" x14ac:dyDescent="0.15">
-      <c r="A40" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+      <c r="A40" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>169</v>
+      </c>
       <c r="D40" s="8">
         <v>31</v>
       </c>
       <c r="E40" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G40" s="7"/>
+      <c r="G40" s="17" t="s">
+        <v>300</v>
+      </c>
       <c r="H40" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J40" s="7"/>
+        <v>302</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>179</v>
+      </c>
       <c r="K40" s="7" t="s">
         <v>25</v>
       </c>
@@ -4304,24 +4370,40 @@
         <v>26</v>
       </c>
       <c r="M40" s="9">
-        <v>9712</v>
-      </c>
-      <c r="N40" s="9"/>
+        <v>9737.0139999999992</v>
+      </c>
+      <c r="N40" s="9">
+        <v>9024.7322810000005</v>
+      </c>
       <c r="O40" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="P40" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="P40" s="7">
+        <v>30000</v>
+      </c>
       <c r="Q40" s="10">
         <v>46002</v>
       </c>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="7"/>
+      <c r="R40" s="10">
+        <v>46176</v>
+      </c>
+      <c r="S40" s="10">
+        <v>46233</v>
+      </c>
+      <c r="T40" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="V40" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="W40" s="15" t="s">
+        <v>304</v>
+      </c>
       <c r="X40" s="7" t="s">
-        <v>240</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.15">
@@ -4577,11 +4659,12 @@
     <hyperlink ref="W14" r:id="rId14" xr:uid="{56EA8146-7375-2940-8CE7-621D3D82E155}"/>
     <hyperlink ref="W15" r:id="rId15" xr:uid="{B991F48F-963A-5548-9E1D-97F06C683698}"/>
     <hyperlink ref="W20" r:id="rId16" xr:uid="{AE74A4E6-305E-5F49-B0FE-9AAB97F6A3DF}"/>
+    <hyperlink ref="W40" r:id="rId17" xr:uid="{58E4C55D-2972-6044-88B9-E8D053273528}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId17"/>
+  <legacyDrawing r:id="rId18"/>
   <tableParts count="1">
-    <tablePart r:id="rId18"/>
+    <tablePart r:id="rId19"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4596,7 +4679,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56A6416-3343-BB45-8BF5-691227B47E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B70C9F-C055-7A4F-93F9-A7FEFFAD449A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36440" yWindow="0" windowWidth="32360" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,12 +36,14 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={DBA8E842-1B69-4E44-955F-86A6656A5A38}</author>
-    <author>tc={2603CD78-4DA2-7245-9496-2BEE29538FD4}</author>
-    <author>tc={D89771A4-99A8-0740-A054-82109EE9B8C1}</author>
+    <author>tc={CC7FC192-DD2F-524F-965B-B519233399BD}</author>
+    <author>tc={EA61046C-C94E-C449-8761-ABD505A37332}</author>
+    <author>tc={9E845984-16BC-D640-8568-DCBC39BD282B}</author>
+    <author>tc={D756854B-3370-2C47-8E59-D458EBCA5109}</author>
+    <author>tc={909B81E5-AB38-BB4F-A77E-C63D2711848A}</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{DBA8E842-1B69-4E44-955F-86A6656A5A38}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{CC7FC192-DD2F-524F-965B-B519233399BD}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -50,7 +52,24 @@
 </t>
       </text>
     </comment>
-    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{2603CD78-4DA2-7245-9496-2BEE29538FD4}">
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{EA61046C-C94E-C449-8761-ABD505A37332}">
+      <text>
+        <t xml:space="preserve">[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    En los casos en que el monto total de inversión informado en el sitio web oficial del RIGI difiere del consignado en la resolución correspondiente a cada proyecto aprobado, se utiliza el monto publicado en el sitio web oficial del régimen.
+</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="2" shapeId="0" xr:uid="{9E845984-16BC-D640-8568-DCBC39BD282B}">
+      <text>
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Se completo los datos de inversión total de los proyectos aprobados con los montos reportados en la resolución respectiva de cada proyecto. En algunos casos los montos reportados difieren en comparación a los reportados en el sitio web oficial del RIGI del gobierno</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="3" shapeId="0" xr:uid="{D756854B-3370-2C47-8E59-D458EBCA5109}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -59,7 +78,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="M3" authorId="2" shapeId="0" xr:uid="{D89771A4-99A8-0740-A054-82109EE9B8C1}">
+    <comment ref="N3" authorId="4" shapeId="0" xr:uid="{909B81E5-AB38-BB4F-A77E-C63D2711848A}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -73,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="309">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -915,9 +934,6 @@
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/344628/20260721</t>
   </si>
   <si>
-    <t>Res. 1015/2026</t>
-  </si>
-  <si>
     <t>Explotación y Producción de Hidrocarburos Líquidos y Gaseosos Costa Adentro</t>
   </si>
   <si>
@@ -999,9 +1015,6 @@
     <t>33-61913055-9</t>
   </si>
   <si>
-    <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución.</t>
-  </si>
-  <si>
     <t>Cobre, Oro y Plata</t>
   </si>
   <si>
@@ -1015,6 +1028,18 @@
   </si>
   <si>
     <t>Antes del anuncio inicial del RIGI, Josemaría ya contaba con una factibilidad de noviembre de 2020, una evaluación ambiental aprobada en abril de 2022, ingeniería, adquisición de equipos de larga entrega y USD 276 millones de gastos de capital durante 2023; Filo del Sol también poseía prefactibilidades y exploración avanzada. Estos antecedentes corresponden a los mismos depósitos y, principalmente, a la actual primera etapa basada en Josemaría. Sin embargo, la sociedad conjunta BHP–Lundin se constituyó en enero de 2025, la primera evaluación técnica unificada apareció en febrero de 2026 y la decisión final de inversión continuaba pendiente después de la aprobación.</t>
+  </si>
+  <si>
+    <t>Monto (mill. USD) - aprobados resolución</t>
+  </si>
+  <si>
+    <t>Expansión Fase 1B</t>
+  </si>
+  <si>
+    <t>Res. 1025/2026</t>
+  </si>
+  <si>
+    <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución. Incluye infraestructura clave para operaciones de minería a cielo abierto: una planta concentradora para el procesamiento de minerales, instalaciones de lixiviación, infraestructura eléctrica, sistemas de suministro de agua, caminos de acceso y alojamientos.</t>
   </si>
 </sst>
 </file>
@@ -1024,7 +1049,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1099,6 +1124,12 @@
       <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1222,21 +1253,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Notas" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1282,7 +1299,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1432,6 +1449,26 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1518,12 +1555,12 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF212529"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1605,6 +1642,20 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color rgb="FF212529"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
@@ -1670,38 +1721,40 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Lucas Ordoñez" id="{F2242E26-5684-4344-B202-B574D4AF1870}" userId="aece5baeefa9fdd6" providerId="Windows Live"/>
   <person displayName="Lucas Sebastian Ordoñez" id="{CC6B0CDD-571C-5947-AB3B-0FE73E1F689E}" userId="S::01OR42856583@campus.economicas.uba.ar::7e5516ec-a921-4253-95aa-4b0e13b66244" providerId="AD"/>
   <person displayName="Lucas Sebastian Ordoñez" id="{2E8DF262-CB25-3049-80AF-0C6513AADFB8}" userId="S::01or42856583@campus.economicas.uba.ar::7e5516ec-a921-4253-95aa-4b0e13b66244" providerId="AD"/>
 </personList>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProyectosIntegrados" displayName="ProyectosIntegrados" ref="A1:X40" headerRowDxfId="26" dataDxfId="0" totalsRowDxfId="25">
-  <tableColumns count="24">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="VPU" dataDxfId="24"/>
-    <tableColumn id="22" xr3:uid="{48F4E9CA-8EE4-9B46-B775-30029B62248E}" name="Descripción_del_proyecto" dataDxfId="23"/>
-    <tableColumn id="19" xr3:uid="{59A3C3BF-E3A1-3748-85BC-5ADA196D8039}" name="Proyectos de exportación estratégica de largo plazo (PEELP)" dataDxfId="22"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id_proyecto" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="empresa" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="titular_proyecto" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{E1C7B229-46A1-4B4F-9ADD-A9E811939D67}" name="CUIT" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="sector" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="subsector" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{3AFF64F9-973D-4A41-865B-D4166A5841A1}" name="actividad_subsector_resolución_MECON" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="provincia" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="localidad_region" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Monto (mill. USD)" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Activos Computables (mill. USD)" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Estado administrativo" dataDxfId="10"/>
-    <tableColumn id="24" xr3:uid="{00D6C894-3563-A741-A5B5-7FF8DB602F8A}" name="Empleos (directos e indirectos)" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="fecha_presentacion" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{D27A2121-7D63-544C-B031-C3DB1A1B8B6A}" name="fecha_adhesion_rigi" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="fecha_publicacion_bo" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="norma_aprobacion" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{B0966B39-0FA3-9146-96DB-BD345771FAC8}" name="Clasificacion_preexistencia_boletin_oficial" dataDxfId="4"/>
-    <tableColumn id="23" xr3:uid="{36F41A70-CDCD-0440-8E79-C4973DF4F4B3}" name="Justificacion_preexistencia_boletin_oficial" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{BC53B1FB-4807-D244-BE0E-F220BF050122}" name="link_norma" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{6C16FCDF-822E-B843-A888-4F4B69680144}" name="Fuentes" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC5949B-99C1-C640-8DA2-C585B697BBE1}" name="ProyectosIntegrados2" displayName="ProyectosIntegrados2" ref="A1:Y40" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
+  <tableColumns count="25">
+    <tableColumn id="2" xr3:uid="{1FB8F74D-9682-B440-94D1-B6000493E00B}" name="VPU" dataDxfId="24"/>
+    <tableColumn id="22" xr3:uid="{5F9EE6EB-2E4C-E743-B117-A1464438FFC7}" name="Descripción_del_proyecto" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{CFDF2429-F95D-3943-82F8-451A000B9F82}" name="Proyectos de exportación estratégica de largo plazo (PEELP)" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{AD64BC74-95BA-9A4E-AC4B-3DE73836DF90}" name="id_proyecto" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{51791E87-341F-3E41-878A-791662F5DBC9}" name="empresa" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{EADE9DE9-6117-8647-8338-D28DBAA6E72A}" name="titular_proyecto" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{904FDB28-DA1F-0547-8978-EB97CA045828}" name="CUIT" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{2D7A2D94-3733-994A-982A-DEDF8271CB6C}" name="sector" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{492831FB-44CE-CB47-B672-3D25B8F10010}" name="subsector" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{2D9EE4A5-6D6B-0047-8C2F-450DC201B187}" name="actividad_subsector_resolución_MECON" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{5BE522C7-9388-8F44-946E-83E19B93BC7A}" name="provincia" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{4E3CB780-5074-FA4F-B98A-31E67E04A07F}" name="localidad_region" dataDxfId="13"/>
+    <tableColumn id="25" xr3:uid="{00D4308B-7D36-6741-B428-F839A6601293}" name="Monto (mill. USD)" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00FC2C60-51B2-5A4E-8D40-F20AEB84CDFF}" name="Monto (mill. USD) - aprobados resolución" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{A666CB24-8E9B-1A47-B550-E880F1AA03B2}" name="Activos Computables (mill. USD)" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{933A8A58-B5F6-224E-82E5-38224B7039BF}" name="Estado administrativo" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{D74832FC-F160-7B4E-B861-458D7BE39728}" name="Empleos (directos e indirectos)" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{1E31A58A-1B53-7345-B5A3-DDC3DE7DC28F}" name="fecha_presentacion" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{2EC6C086-DEA7-7148-A622-467B3FC9C8E5}" name="fecha_adhesion_rigi" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{1FBCC2F8-A44E-EE4B-B919-FD06CDA903B1}" name="fecha_publicacion_bo" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{AB9E3FD5-D9E1-FB4C-805E-4DC1E2E4F884}" name="norma_aprobacion" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{32A3F66C-F383-6A4F-BC9B-CE60E9775140}" name="Clasificacion_preexistencia_boletin_oficial" dataDxfId="3"/>
+    <tableColumn id="23" xr3:uid="{8FFE7748-3D7D-F44F-9EE0-37998D10E3B7}" name="Justificacion_preexistencia_boletin_oficial" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{B5F0282B-C127-7C40-86CC-663CD39DAAF5}" name="link_norma" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{4245686F-374C-B840-9963-4B9AF6D5BD62}" name="Fuentes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1883,15 +1936,22 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E1" dT="2026-06-15T21:16:51.15" personId="{CC6B0CDD-571C-5947-AB3B-0FE73E1F689E}" id="{DBA8E842-1B69-4E44-955F-86A6656A5A38}">
+  <threadedComment ref="E1" dT="2026-06-15T21:16:51.15" personId="{CC6B0CDD-571C-5947-AB3B-0FE73E1F689E}" id="{CC7FC192-DD2F-524F-965B-B519233399BD}">
     <text xml:space="preserve">La fuente de datos de esta variable es el tracker de GLOBARIS
 </text>
   </threadedComment>
-  <threadedComment ref="P1" dT="2026-06-15T21:15:54.67" personId="{CC6B0CDD-571C-5947-AB3B-0FE73E1F689E}" id="{2603CD78-4DA2-7245-9496-2BEE29538FD4}">
+  <threadedComment ref="M1" dT="2026-07-30T19:12:39.35" personId="{F2242E26-5684-4344-B202-B574D4AF1870}" id="{EA61046C-C94E-C449-8761-ABD505A37332}">
+    <text xml:space="preserve">En los casos en que el monto total de inversión informado en el sitio web oficial del RIGI difiere del consignado en la resolución correspondiente a cada proyecto aprobado, se utiliza el monto publicado en el sitio web oficial del régimen.
+</text>
+  </threadedComment>
+  <threadedComment ref="N1" dT="2026-07-30T19:10:18.02" personId="{F2242E26-5684-4344-B202-B574D4AF1870}" id="{9E845984-16BC-D640-8568-DCBC39BD282B}">
+    <text>Se completo los datos de inversión total de los proyectos aprobados con los montos reportados en la resolución respectiva de cada proyecto. En algunos casos los montos reportados difieren en comparación a los reportados en el sitio web oficial del RIGI del gobierno</text>
+  </threadedComment>
+  <threadedComment ref="Q1" dT="2026-06-15T21:15:54.67" personId="{CC6B0CDD-571C-5947-AB3B-0FE73E1F689E}" id="{D756854B-3370-2C47-8E59-D458EBCA5109}">
     <text xml:space="preserve">La fuente de datos de esta variable es el monitor del RIGI del MECON
 </text>
   </threadedComment>
-  <threadedComment ref="M3" dT="2026-06-09T13:10:11.61" personId="{2E8DF262-CB25-3049-80AF-0C6513AADFB8}" id="{D89771A4-99A8-0740-A054-82109EE9B8C1}">
+  <threadedComment ref="N3" dT="2026-06-09T13:10:11.61" personId="{2E8DF262-CB25-3049-80AF-0C6513AADFB8}" id="{909B81E5-AB38-BB4F-A77E-C63D2711848A}">
     <text xml:space="preserve">Que el solicitante declaró que el proyecto implicará una inversión total de entre dólares estadounidenses dos mil novecientos millones (USD 2.900.000.000) y dólares estadounidenses tres mil doscientos millones (USD 3.200.000.000). Se computa el promedio
 </text>
   </threadedComment>
@@ -1900,13 +1960,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="94.33203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="94.33203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>196</v>
       </c>
@@ -1914,7 +1974,7 @@
         <v>183</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1947,45 +2007,48 @@
         <v>146</v>
       </c>
       <c r="N1" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="X1" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="30" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>169</v>
@@ -2018,48 +2081,51 @@
         <v>12</v>
       </c>
       <c r="M2" s="9">
+        <v>15156</v>
+      </c>
+      <c r="N2" s="9">
         <v>6878</v>
       </c>
-      <c r="N2" s="9">
+      <c r="O2" s="9">
         <v>2825</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="7">
+      <c r="Q2" s="7">
         <v>836</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="R2" s="10">
         <v>45617</v>
       </c>
-      <c r="R2" s="10">
+      <c r="S2" s="10">
         <v>45775</v>
       </c>
-      <c r="S2" s="10">
+      <c r="T2" s="10">
         <v>45776</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="V2" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="W2" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="Y2" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>176</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>169</v>
@@ -2092,48 +2158,51 @@
         <v>12</v>
       </c>
       <c r="M3" s="9">
+        <v>2900</v>
+      </c>
+      <c r="N3" s="9">
         <v>3050</v>
       </c>
-      <c r="N3" s="9">
+      <c r="O3" s="9">
         <v>2486</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="7">
+      <c r="Q3" s="7">
         <v>3108</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="R3" s="10">
         <v>45611</v>
       </c>
-      <c r="R3" s="10">
+      <c r="S3" s="10">
         <v>45722</v>
       </c>
-      <c r="S3" s="10">
+      <c r="T3" s="10">
         <v>45736</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="12" t="s">
+      <c r="X3" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
         <v>181</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>169</v>
@@ -2169,45 +2238,48 @@
         <v>2672.1709999999998</v>
       </c>
       <c r="N4" s="9">
+        <v>2672.1709999999998</v>
+      </c>
+      <c r="O4" s="9">
         <v>2354</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="P4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="7">
+      <c r="Q4" s="7">
         <v>7391</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="R4" s="10">
         <v>45849</v>
       </c>
-      <c r="R4" s="10">
+      <c r="S4" s="10">
         <v>45925</v>
       </c>
-      <c r="S4" s="10">
+      <c r="T4" s="10">
         <v>45943</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="U4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="V4" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="W4" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="W4" s="12" t="s">
+      <c r="X4" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="Y4" s="7" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="60" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
         <v>185</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>169</v>
@@ -2243,40 +2315,43 @@
         <v>2744</v>
       </c>
       <c r="N5" s="9">
+        <v>2744</v>
+      </c>
+      <c r="O5" s="9">
         <v>2299</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="P5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="7">
+      <c r="Q5" s="7">
         <v>1985</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="R5" s="10">
         <v>45713</v>
       </c>
-      <c r="R5" s="10">
+      <c r="S5" s="10">
         <v>45796</v>
       </c>
-      <c r="S5" s="10">
+      <c r="T5" s="10">
         <v>45807</v>
       </c>
-      <c r="T5" s="7" t="s">
+      <c r="U5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="U5" s="7" t="s">
+      <c r="V5" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="V5" s="7" t="s">
+      <c r="W5" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="W5" s="12" t="s">
+      <c r="X5" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="X5" s="7" t="s">
+      <c r="Y5" s="7" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>49</v>
       </c>
@@ -2314,48 +2389,51 @@
         <v>26</v>
       </c>
       <c r="M6" s="9">
-        <v>613.42999999999995</v>
+        <v>891</v>
       </c>
       <c r="N6" s="9">
         <v>613.42999999999995</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="O6" s="9">
+        <v>613.42999999999995</v>
+      </c>
+      <c r="P6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="7">
+      <c r="Q6" s="7">
         <v>6300</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="R6" s="10">
         <v>45967</v>
       </c>
-      <c r="R6" s="10">
+      <c r="S6" s="10">
         <v>46155</v>
       </c>
-      <c r="S6" s="10">
+      <c r="T6" s="10">
         <v>46168</v>
       </c>
-      <c r="T6" s="7" t="s">
+      <c r="U6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U6" s="7" t="s">
+      <c r="V6" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V6" s="7" t="s">
+      <c r="W6" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="W6" s="12" t="s">
+      <c r="X6" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="X6" s="7" t="s">
+      <c r="Y6" s="7" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
         <v>191</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>182</v>
@@ -2388,48 +2466,51 @@
         <v>26</v>
       </c>
       <c r="M7" s="9">
-        <v>519.64700000000005</v>
+        <v>665</v>
       </c>
       <c r="N7" s="9">
         <v>519.64700000000005</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="O7" s="9">
+        <v>519.64700000000005</v>
+      </c>
+      <c r="P7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P7" s="7">
+      <c r="Q7" s="7">
         <v>4500</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="R7" s="10">
         <v>45814</v>
       </c>
-      <c r="R7" s="10">
+      <c r="S7" s="10">
         <v>45988</v>
       </c>
-      <c r="S7" s="10">
+      <c r="T7" s="10">
         <v>46035</v>
       </c>
-      <c r="T7" s="7" t="s">
+      <c r="U7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="U7" s="7" t="s">
+      <c r="V7" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V7" s="13" t="s">
+      <c r="W7" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="W7" s="12" t="s">
+      <c r="X7" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="X7" s="7" t="s">
+      <c r="Y7" s="7" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
         <v>192</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>182</v>
@@ -2465,45 +2546,48 @@
         <v>550</v>
       </c>
       <c r="N8" s="9">
+        <v>550</v>
+      </c>
+      <c r="O8" s="9">
         <v>513.37199999999996</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="P8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="7">
+      <c r="Q8" s="7">
         <v>7535</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="R8" s="10">
         <v>45957</v>
       </c>
-      <c r="R8" s="10">
+      <c r="S8" s="10">
         <v>46142</v>
       </c>
-      <c r="S8" s="10">
+      <c r="T8" s="10">
         <v>46154</v>
       </c>
-      <c r="T8" s="7" t="s">
+      <c r="U8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="U8" s="7" t="s">
+      <c r="V8" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="V8" s="7" t="s">
+      <c r="W8" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="W8" s="12" t="s">
+      <c r="X8" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="X8" s="7" t="s">
+      <c r="Y8" s="7" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>182</v>
@@ -2536,43 +2620,46 @@
         <v>21</v>
       </c>
       <c r="M9" s="9">
-        <v>481.7</v>
+        <v>764</v>
       </c>
       <c r="N9" s="9">
         <v>481.7</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="O9" s="9">
+        <v>481.7</v>
+      </c>
+      <c r="P9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="7">
+      <c r="Q9" s="7">
         <v>2013</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="R9" s="10">
         <v>45981</v>
       </c>
-      <c r="R9" s="10">
+      <c r="S9" s="10">
         <v>46080</v>
       </c>
-      <c r="S9" s="10">
+      <c r="T9" s="10">
         <v>46149</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="U9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="U9" s="7" t="s">
+      <c r="V9" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V9" s="7" t="s">
+      <c r="W9" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="W9" s="15" t="s">
+      <c r="X9" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="X9" s="7" t="s">
+      <c r="Y9" s="7" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="75" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:25" ht="75" x14ac:dyDescent="0.15">
       <c r="A10" s="14" t="s">
         <v>203</v>
       </c>
@@ -2610,48 +2697,51 @@
         <v>26</v>
       </c>
       <c r="M10" s="9">
-        <v>380.11599999999999</v>
+        <v>436</v>
       </c>
       <c r="N10" s="9">
         <v>380.11599999999999</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="9">
+        <v>380.11599999999999</v>
+      </c>
+      <c r="P10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P10" s="7">
+      <c r="Q10" s="7">
         <v>1048</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="R10" s="10">
         <v>45873</v>
       </c>
-      <c r="R10" s="10">
+      <c r="S10" s="10">
         <v>46050</v>
       </c>
-      <c r="S10" s="10">
+      <c r="T10" s="10">
         <v>46111</v>
       </c>
-      <c r="T10" s="7" t="s">
+      <c r="U10" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="U10" s="14" t="s">
+      <c r="V10" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="V10" s="7" t="s">
+      <c r="W10" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="W10" s="15" t="s">
+      <c r="X10" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="X10" s="7" t="s">
+      <c r="Y10" s="7" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="75" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:25" ht="75" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>182</v>
@@ -2689,43 +2779,46 @@
       <c r="N11" s="9">
         <v>286.27800000000002</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="9">
+        <v>286.27800000000002</v>
+      </c>
+      <c r="P11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P11" s="7">
+      <c r="Q11" s="7">
         <v>3800</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="R11" s="10">
         <v>45638</v>
       </c>
-      <c r="R11" s="10">
+      <c r="S11" s="10">
         <v>45807</v>
       </c>
-      <c r="S11" s="10">
+      <c r="T11" s="10">
         <v>45859</v>
       </c>
-      <c r="T11" s="7" t="s">
+      <c r="U11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="U11" s="7" t="s">
+      <c r="V11" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V11" s="7" t="s">
+      <c r="W11" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="W11" s="11" t="s">
+      <c r="X11" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="X11" s="7" t="s">
+      <c r="Y11" s="7" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="60" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:25" ht="60" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
         <v>210</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>182</v>
@@ -2763,43 +2856,46 @@
       <c r="N12" s="9">
         <v>276.89999999999998</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="O12" s="9">
+        <v>276.89999999999998</v>
+      </c>
+      <c r="P12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P12" s="7">
+      <c r="Q12" s="7">
         <v>9700</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="R12" s="10">
         <v>45757</v>
       </c>
-      <c r="R12" s="10">
+      <c r="S12" s="10">
         <v>45953</v>
       </c>
-      <c r="S12" s="10">
+      <c r="T12" s="10">
         <v>45980</v>
       </c>
-      <c r="T12" s="7" t="s">
+      <c r="U12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="U12" s="7" t="s">
+      <c r="V12" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V12" s="7" t="s">
+      <c r="W12" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="W12" s="12" t="s">
+      <c r="X12" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="X12" s="7" t="s">
+      <c r="Y12" s="7" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="120" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:25" ht="120" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>182</v>
@@ -2835,45 +2931,48 @@
         <v>275.58999999999997</v>
       </c>
       <c r="N13" s="9">
+        <v>275.58999999999997</v>
+      </c>
+      <c r="O13" s="9">
         <v>255.11199999999999</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="P13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P13" s="7">
+      <c r="Q13" s="7">
         <v>165</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="R13" s="10">
         <v>45656</v>
       </c>
-      <c r="R13" s="10">
+      <c r="S13" s="10">
         <v>45863</v>
       </c>
-      <c r="S13" s="10">
+      <c r="T13" s="10">
         <v>45895</v>
       </c>
-      <c r="T13" s="7" t="s">
+      <c r="U13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="U13" s="7" t="s">
+      <c r="V13" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V13" s="7" t="s">
+      <c r="W13" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="W13" s="12" t="s">
+      <c r="X13" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="X13" s="7" t="s">
+      <c r="Y13" s="7" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="120" x14ac:dyDescent="0.15">
-      <c r="A14" s="7" t="s">
-        <v>191</v>
+    <row r="14" spans="1:25" ht="120" x14ac:dyDescent="0.15">
+      <c r="A14" s="17" t="s">
+        <v>306</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>182</v>
@@ -2906,48 +3005,51 @@
         <v>21</v>
       </c>
       <c r="M14" s="9">
-        <v>251.321</v>
+        <v>531</v>
       </c>
       <c r="N14" s="9">
         <v>251.321</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="O14" s="9">
+        <v>251.321</v>
+      </c>
+      <c r="P14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="7">
+      <c r="Q14" s="7">
         <v>1273</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="R14" s="10">
         <v>45898</v>
       </c>
-      <c r="R14" s="10">
+      <c r="S14" s="10">
         <v>46106</v>
       </c>
-      <c r="S14" s="10">
+      <c r="T14" s="10">
         <v>46112</v>
       </c>
-      <c r="T14" s="7" t="s">
+      <c r="U14" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="U14" s="7" t="s">
+      <c r="V14" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="V14" s="7" t="s">
+      <c r="W14" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="W14" s="12" t="s">
+      <c r="X14" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="X14" s="7" t="s">
+      <c r="Y14" s="7" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>71</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>182</v>
@@ -2980,48 +3082,51 @@
         <v>21</v>
       </c>
       <c r="M15" s="9">
-        <v>217.09</v>
+        <v>292</v>
       </c>
       <c r="N15" s="9">
         <v>217.09</v>
       </c>
-      <c r="O15" s="7" t="s">
+      <c r="O15" s="9">
+        <v>217.09</v>
+      </c>
+      <c r="P15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P15" s="7">
+      <c r="Q15" s="7">
         <v>670</v>
       </c>
-      <c r="Q15" s="10">
+      <c r="R15" s="10">
         <v>45594</v>
       </c>
-      <c r="R15" s="10">
+      <c r="S15" s="10">
         <v>45855</v>
       </c>
-      <c r="S15" s="10">
+      <c r="T15" s="10">
         <v>45896</v>
       </c>
-      <c r="T15" s="7" t="s">
+      <c r="U15" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="U15" s="7" t="s">
+      <c r="V15" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V15" s="7" t="s">
+      <c r="W15" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="W15" s="12" t="s">
+      <c r="X15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="X15" s="7" t="s">
+      <c r="Y15" s="7" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>182</v>
@@ -3052,43 +3157,46 @@
         <v>26</v>
       </c>
       <c r="M16" s="9">
-        <v>211.6</v>
+        <v>211</v>
       </c>
       <c r="N16" s="9">
-        <v>211.6</v>
-      </c>
-      <c r="O16" s="7" t="s">
+        <v>211.60007200000001</v>
+      </c>
+      <c r="O16" s="9">
+        <v>211.60007200000001</v>
+      </c>
+      <c r="P16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P16" s="7">
+      <c r="Q16" s="7">
         <v>384</v>
       </c>
-      <c r="Q16" s="10">
+      <c r="R16" s="10">
         <v>45590</v>
       </c>
-      <c r="R16" s="10">
+      <c r="S16" s="10">
         <v>45642</v>
       </c>
-      <c r="S16" s="10">
+      <c r="T16" s="10">
         <v>45664</v>
       </c>
-      <c r="T16" s="7" t="s">
+      <c r="U16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="U16" s="7" t="s">
+      <c r="V16" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="V16" s="13" t="s">
+      <c r="W16" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="W16" s="12" t="s">
+      <c r="X16" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="X16" s="7" t="s">
+      <c r="Y16" s="7" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
         <v>78</v>
       </c>
@@ -3120,25 +3228,28 @@
       <c r="M17" s="9">
         <v>726</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="7" t="s">
+      <c r="N17" s="9">
+        <v>726</v>
+      </c>
+      <c r="O17" s="9"/>
+      <c r="P17" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="10">
+      <c r="Q17" s="7"/>
+      <c r="R17" s="10">
         <v>45671</v>
       </c>
-      <c r="R17" s="10"/>
       <c r="S17" s="10"/>
-      <c r="T17" s="7"/>
+      <c r="T17" s="10"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="7" t="s">
+      <c r="W17" s="7"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
         <v>81</v>
       </c>
@@ -3170,25 +3281,28 @@
       <c r="M18" s="9">
         <v>232</v>
       </c>
-      <c r="N18" s="9"/>
-      <c r="O18" s="7" t="s">
+      <c r="N18" s="9">
+        <v>232</v>
+      </c>
+      <c r="O18" s="9"/>
+      <c r="P18" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="10">
+      <c r="Q18" s="7"/>
+      <c r="R18" s="10">
         <v>45874</v>
       </c>
-      <c r="R18" s="10"/>
       <c r="S18" s="10"/>
-      <c r="T18" s="7"/>
+      <c r="T18" s="10"/>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="7" t="s">
+      <c r="W18" s="7"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="14" t="s">
         <v>86</v>
       </c>
@@ -3220,25 +3334,28 @@
       <c r="M19" s="9">
         <v>12000</v>
       </c>
-      <c r="N19" s="9"/>
-      <c r="O19" s="7" t="s">
+      <c r="N19" s="9">
+        <v>12000</v>
+      </c>
+      <c r="O19" s="9"/>
+      <c r="P19" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="10">
+      <c r="Q19" s="7"/>
+      <c r="R19" s="10">
         <v>45771</v>
       </c>
-      <c r="R19" s="10"/>
       <c r="S19" s="10"/>
-      <c r="T19" s="7"/>
+      <c r="T19" s="10"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="7" t="s">
+      <c r="W19" s="7"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="45" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
         <v>219</v>
       </c>
@@ -3276,43 +3393,46 @@
         <v>21</v>
       </c>
       <c r="M20" s="9">
-        <v>1166.6777259999999</v>
+        <v>1241</v>
       </c>
       <c r="N20" s="9">
         <v>1166.6777259999999</v>
       </c>
-      <c r="O20" s="7" t="s">
+      <c r="O20" s="9">
+        <v>1166.6777259999999</v>
+      </c>
+      <c r="P20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P20" s="7">
+      <c r="Q20" s="7">
         <v>1787</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="R20" s="10">
         <v>45795</v>
       </c>
-      <c r="R20" s="10">
+      <c r="S20" s="10">
         <v>46151</v>
       </c>
-      <c r="S20" s="10">
+      <c r="T20" s="10">
         <v>46177</v>
       </c>
-      <c r="T20" s="7" t="s">
+      <c r="U20" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="U20" s="7" t="s">
+      <c r="V20" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="V20" s="7" t="s">
+      <c r="W20" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="W20" s="15" t="s">
+      <c r="X20" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="X20" s="7" t="s">
+      <c r="Y20" s="7" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="14" t="s">
         <v>92</v>
       </c>
@@ -3344,25 +3464,28 @@
       <c r="M21" s="9">
         <v>380</v>
       </c>
-      <c r="N21" s="9"/>
-      <c r="O21" s="7" t="s">
+      <c r="N21" s="9">
+        <v>380</v>
+      </c>
+      <c r="O21" s="9"/>
+      <c r="P21" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="10">
+      <c r="Q21" s="7"/>
+      <c r="R21" s="10">
         <v>45859</v>
       </c>
-      <c r="R21" s="10"/>
       <c r="S21" s="10"/>
-      <c r="T21" s="7"/>
+      <c r="T21" s="10"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="7" t="s">
+      <c r="W21" s="7"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
         <v>95</v>
       </c>
@@ -3394,25 +3517,28 @@
       <c r="M22" s="9">
         <v>9500</v>
       </c>
-      <c r="N22" s="9"/>
-      <c r="O22" s="7" t="s">
+      <c r="N22" s="9">
+        <v>9500</v>
+      </c>
+      <c r="O22" s="9"/>
+      <c r="P22" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="10">
+      <c r="Q22" s="7"/>
+      <c r="R22" s="10">
         <v>45887</v>
       </c>
-      <c r="R22" s="10"/>
       <c r="S22" s="10"/>
-      <c r="T22" s="7"/>
+      <c r="T22" s="10"/>
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="7" t="s">
+      <c r="W22" s="7"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
         <v>98</v>
       </c>
@@ -3444,25 +3570,28 @@
       <c r="M23" s="9">
         <v>13800</v>
       </c>
-      <c r="N23" s="9"/>
-      <c r="O23" s="7" t="s">
+      <c r="N23" s="9">
+        <v>13800</v>
+      </c>
+      <c r="O23" s="9"/>
+      <c r="P23" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="10">
+      <c r="Q23" s="7"/>
+      <c r="R23" s="10">
         <v>46175</v>
       </c>
-      <c r="R23" s="10"/>
       <c r="S23" s="10"/>
-      <c r="T23" s="7"/>
+      <c r="T23" s="10"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="7" t="s">
+      <c r="W23" s="7"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
         <v>136</v>
       </c>
@@ -3494,30 +3623,33 @@
       <c r="M24" s="9">
         <v>2400</v>
       </c>
-      <c r="N24" s="9"/>
-      <c r="O24" s="7" t="s">
+      <c r="N24" s="9">
+        <v>2400</v>
+      </c>
+      <c r="O24" s="9"/>
+      <c r="P24" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="10">
+      <c r="Q24" s="7"/>
+      <c r="R24" s="10">
         <v>46136</v>
       </c>
-      <c r="R24" s="10"/>
       <c r="S24" s="10"/>
-      <c r="T24" s="7"/>
+      <c r="T24" s="10"/>
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="7" t="s">
+      <c r="W24" s="7"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:25" ht="90" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
         <v>263</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>182</v>
@@ -3553,40 +3685,43 @@
         <v>1300</v>
       </c>
       <c r="N25" s="9">
+        <v>1300</v>
+      </c>
+      <c r="O25" s="9">
         <v>955</v>
       </c>
-      <c r="O25" s="7" t="s">
+      <c r="P25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P25" s="7">
+      <c r="Q25" s="7">
         <v>2489</v>
       </c>
-      <c r="Q25" s="10">
+      <c r="R25" s="10">
         <v>45950</v>
       </c>
-      <c r="R25" s="10">
+      <c r="S25" s="10">
         <v>46174</v>
       </c>
-      <c r="S25" s="10">
+      <c r="T25" s="10">
         <v>46198</v>
       </c>
-      <c r="T25" s="7" t="s">
+      <c r="U25" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="U25" s="7" t="s">
+      <c r="V25" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="V25" s="7" t="s">
+      <c r="W25" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="W25" s="12" t="s">
+      <c r="X25" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="X25" s="7" t="s">
+      <c r="Y25" s="7" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
         <v>140</v>
       </c>
@@ -3618,25 +3753,28 @@
       <c r="M26" s="9">
         <v>1151</v>
       </c>
-      <c r="N26" s="9"/>
-      <c r="O26" s="7" t="s">
+      <c r="N26" s="9">
+        <v>1151</v>
+      </c>
+      <c r="O26" s="9"/>
+      <c r="P26" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="10">
+      <c r="Q26" s="7"/>
+      <c r="R26" s="10">
         <v>46111</v>
       </c>
-      <c r="R26" s="10"/>
       <c r="S26" s="10"/>
-      <c r="T26" s="7"/>
+      <c r="T26" s="10"/>
       <c r="U26" s="7"/>
       <c r="V26" s="7"/>
       <c r="W26" s="7"/>
-      <c r="X26" s="7" t="s">
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
         <v>149</v>
       </c>
@@ -3668,25 +3806,28 @@
       <c r="M27" s="9">
         <v>25000</v>
       </c>
-      <c r="N27" s="9"/>
-      <c r="O27" s="7" t="s">
+      <c r="N27" s="9">
+        <v>25000</v>
+      </c>
+      <c r="O27" s="9"/>
+      <c r="P27" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="10">
+      <c r="Q27" s="7"/>
+      <c r="R27" s="10">
         <v>46157</v>
       </c>
-      <c r="R27" s="10"/>
       <c r="S27" s="10"/>
-      <c r="T27" s="7"/>
+      <c r="T27" s="10"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
-      <c r="X27" s="7" t="s">
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
         <v>126</v>
       </c>
@@ -3718,25 +3859,28 @@
       <c r="M28" s="9">
         <v>1000</v>
       </c>
-      <c r="N28" s="9"/>
-      <c r="O28" s="7" t="s">
+      <c r="N28" s="9">
+        <v>1000</v>
+      </c>
+      <c r="O28" s="9"/>
+      <c r="P28" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="10">
+      <c r="Q28" s="7"/>
+      <c r="R28" s="10">
         <v>46157</v>
       </c>
-      <c r="R28" s="10"/>
       <c r="S28" s="10"/>
-      <c r="T28" s="7"/>
+      <c r="T28" s="10"/>
       <c r="U28" s="7"/>
       <c r="V28" s="7"/>
       <c r="W28" s="7"/>
-      <c r="X28" s="7" t="s">
+      <c r="X28" s="7"/>
+      <c r="Y28" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="14" t="s">
         <v>128</v>
       </c>
@@ -3768,25 +3912,28 @@
       <c r="M29" s="9">
         <v>273</v>
       </c>
-      <c r="N29" s="9"/>
-      <c r="O29" s="7" t="s">
+      <c r="N29" s="9">
+        <v>273</v>
+      </c>
+      <c r="O29" s="9"/>
+      <c r="P29" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="10">
+      <c r="Q29" s="7"/>
+      <c r="R29" s="10">
         <v>45717</v>
       </c>
-      <c r="R29" s="10"/>
       <c r="S29" s="10"/>
-      <c r="T29" s="7"/>
+      <c r="T29" s="10"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
-      <c r="X29" s="7" t="s">
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
         <v>132</v>
       </c>
@@ -3818,25 +3965,28 @@
       <c r="M30" s="9">
         <v>360</v>
       </c>
-      <c r="N30" s="9"/>
-      <c r="O30" s="7" t="s">
+      <c r="N30" s="9">
+        <v>360</v>
+      </c>
+      <c r="O30" s="9"/>
+      <c r="P30" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="10">
+      <c r="Q30" s="7"/>
+      <c r="R30" s="10">
         <v>46099</v>
       </c>
-      <c r="R30" s="10"/>
       <c r="S30" s="10"/>
-      <c r="T30" s="7"/>
+      <c r="T30" s="10"/>
       <c r="U30" s="7"/>
       <c r="V30" s="7"/>
       <c r="W30" s="7"/>
-      <c r="X30" s="7" t="s">
+      <c r="X30" s="7"/>
+      <c r="Y30" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
         <v>134</v>
       </c>
@@ -3868,25 +4018,28 @@
       <c r="M31" s="9">
         <v>4000</v>
       </c>
-      <c r="N31" s="9"/>
-      <c r="O31" s="7" t="s">
+      <c r="N31" s="9">
+        <v>4000</v>
+      </c>
+      <c r="O31" s="9"/>
+      <c r="P31" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="10">
+      <c r="Q31" s="7"/>
+      <c r="R31" s="10">
         <v>45887</v>
       </c>
-      <c r="R31" s="10"/>
       <c r="S31" s="10"/>
-      <c r="T31" s="7"/>
+      <c r="T31" s="10"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="7" t="s">
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
         <v>100</v>
       </c>
@@ -3918,25 +4071,28 @@
       <c r="M32" s="9">
         <v>200</v>
       </c>
-      <c r="N32" s="9"/>
-      <c r="O32" s="7" t="s">
+      <c r="N32" s="9">
+        <v>200</v>
+      </c>
+      <c r="O32" s="9"/>
+      <c r="P32" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="10" t="s">
+      <c r="Q32" s="7"/>
+      <c r="R32" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="R32" s="10"/>
       <c r="S32" s="10"/>
-      <c r="T32" s="7"/>
+      <c r="T32" s="10"/>
       <c r="U32" s="7"/>
       <c r="V32" s="7"/>
       <c r="W32" s="7"/>
-      <c r="X32" s="7" t="s">
+      <c r="X32" s="7"/>
+      <c r="Y32" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="7" t="s">
         <v>105</v>
       </c>
@@ -3968,25 +4124,28 @@
       <c r="M33" s="9">
         <v>206</v>
       </c>
-      <c r="N33" s="9"/>
-      <c r="O33" s="7" t="s">
+      <c r="N33" s="9">
+        <v>206</v>
+      </c>
+      <c r="O33" s="9"/>
+      <c r="P33" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="10">
+      <c r="Q33" s="7"/>
+      <c r="R33" s="10">
         <v>45805</v>
       </c>
-      <c r="R33" s="10"/>
       <c r="S33" s="10"/>
-      <c r="T33" s="7"/>
+      <c r="T33" s="10"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
-      <c r="X33" s="7" t="s">
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
         <v>108</v>
       </c>
@@ -4018,25 +4177,28 @@
       <c r="M34" s="9">
         <v>6391</v>
       </c>
-      <c r="N34" s="9"/>
-      <c r="O34" s="7" t="s">
+      <c r="N34" s="9">
+        <v>6391</v>
+      </c>
+      <c r="O34" s="9"/>
+      <c r="P34" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="10">
+      <c r="Q34" s="7"/>
+      <c r="R34" s="10">
         <v>46118</v>
       </c>
-      <c r="R34" s="10"/>
       <c r="S34" s="10"/>
-      <c r="T34" s="7"/>
+      <c r="T34" s="10"/>
       <c r="U34" s="7"/>
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
-      <c r="X34" s="7" t="s">
+      <c r="X34" s="7"/>
+      <c r="Y34" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="7" t="s">
         <v>111</v>
       </c>
@@ -4068,30 +4230,33 @@
       <c r="M35" s="9">
         <v>4245</v>
       </c>
-      <c r="N35" s="9"/>
-      <c r="O35" s="7" t="s">
+      <c r="N35" s="9">
+        <v>4245</v>
+      </c>
+      <c r="O35" s="9"/>
+      <c r="P35" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="10">
+      <c r="Q35" s="7"/>
+      <c r="R35" s="10">
         <v>46081</v>
       </c>
-      <c r="R35" s="10"/>
       <c r="S35" s="10"/>
-      <c r="T35" s="7"/>
+      <c r="T35" s="10"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
       <c r="W35" s="7"/>
-      <c r="X35" s="7" t="s">
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:25" ht="90" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
         <v>270</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>169</v>
@@ -4106,7 +4271,7 @@
         <v>115</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>165</v>
@@ -4115,7 +4280,7 @@
         <v>165</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>89</v>
@@ -4124,43 +4289,46 @@
         <v>12</v>
       </c>
       <c r="M36" s="9">
-        <v>4521</v>
+        <v>4522</v>
       </c>
       <c r="N36" s="9">
         <v>4521</v>
       </c>
-      <c r="O36" s="7" t="s">
+      <c r="O36" s="9">
+        <v>4521</v>
+      </c>
+      <c r="P36" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P36" s="7">
+      <c r="Q36" s="7">
         <v>1733</v>
       </c>
-      <c r="Q36" s="10">
+      <c r="R36" s="10">
         <v>46090</v>
       </c>
-      <c r="R36" s="10">
+      <c r="S36" s="10">
         <v>46198</v>
       </c>
-      <c r="S36" s="10">
+      <c r="T36" s="10">
         <v>46224</v>
       </c>
-      <c r="T36" s="7" t="s">
-        <v>273</v>
-      </c>
       <c r="U36" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="V36" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="V36" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="W36" s="7" t="s">
+      <c r="W36" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="X36" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="X36" s="7" t="s">
+      <c r="Y36" s="7" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
         <v>116</v>
       </c>
@@ -4192,25 +4360,28 @@
       <c r="M37" s="9">
         <v>845</v>
       </c>
-      <c r="N37" s="9"/>
-      <c r="O37" s="7" t="s">
+      <c r="N37" s="9">
+        <v>845</v>
+      </c>
+      <c r="O37" s="9"/>
+      <c r="P37" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="10">
+      <c r="Q37" s="7"/>
+      <c r="R37" s="10">
         <v>45595</v>
       </c>
-      <c r="R37" s="10"/>
       <c r="S37" s="10"/>
-      <c r="T37" s="7"/>
+      <c r="T37" s="10"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
-      <c r="X37" s="7" t="s">
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="7" t="s">
         <v>119</v>
       </c>
@@ -4242,30 +4413,33 @@
       <c r="M38" s="9">
         <v>818</v>
       </c>
-      <c r="N38" s="9"/>
-      <c r="O38" s="7" t="s">
+      <c r="N38" s="9">
+        <v>818</v>
+      </c>
+      <c r="O38" s="9"/>
+      <c r="P38" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="10">
+      <c r="Q38" s="7"/>
+      <c r="R38" s="10">
         <v>45758</v>
       </c>
-      <c r="R38" s="10"/>
       <c r="S38" s="10"/>
-      <c r="T38" s="7"/>
+      <c r="T38" s="10"/>
       <c r="U38" s="7"/>
       <c r="V38" s="7"/>
       <c r="W38" s="7"/>
-      <c r="X38" s="7" t="s">
+      <c r="X38" s="7"/>
+      <c r="Y38" s="7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:25" ht="90" x14ac:dyDescent="0.15">
       <c r="A39" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="8">
@@ -4278,7 +4452,7 @@
         <v>122</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>19</v>
@@ -4299,45 +4473,48 @@
         <v>710</v>
       </c>
       <c r="N39" s="9">
+        <v>710</v>
+      </c>
+      <c r="O39" s="9">
         <v>594.13599999999997</v>
       </c>
-      <c r="O39" s="7" t="s">
+      <c r="P39" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P39" s="7">
+      <c r="Q39" s="7">
         <v>4406</v>
       </c>
-      <c r="Q39" s="10">
+      <c r="R39" s="10">
         <v>46063</v>
       </c>
-      <c r="R39" s="10">
+      <c r="S39" s="10">
         <v>46206</v>
       </c>
-      <c r="S39" s="10">
+      <c r="T39" s="10">
         <v>46232</v>
       </c>
-      <c r="T39" s="7" t="s">
-        <v>281</v>
-      </c>
       <c r="U39" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="V39" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="V39" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="W39" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="X39" s="7" t="s">
+      <c r="W39" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="X39" s="15" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" ht="90" x14ac:dyDescent="0.15">
+      <c r="Y39" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="90" x14ac:dyDescent="0.15">
       <c r="A40" s="17" t="s">
         <v>123</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>169</v>
@@ -4352,13 +4529,13 @@
         <v>125</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J40" s="14" t="s">
         <v>179</v>
@@ -4373,40 +4550,43 @@
         <v>9737.0139999999992</v>
       </c>
       <c r="N40" s="9">
+        <v>9737.0139999999992</v>
+      </c>
+      <c r="O40" s="9">
         <v>9024.7322810000005</v>
       </c>
-      <c r="O40" s="7" t="s">
+      <c r="P40" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="P40" s="7">
-        <v>30000</v>
-      </c>
-      <c r="Q40" s="10">
+      <c r="Q40" s="7">
+        <v>31700</v>
+      </c>
+      <c r="R40" s="10">
         <v>46002</v>
       </c>
-      <c r="R40" s="10">
+      <c r="S40" s="10">
         <v>46176</v>
       </c>
-      <c r="S40" s="10">
+      <c r="T40" s="10">
         <v>46233</v>
       </c>
-      <c r="T40" s="7" t="s">
+      <c r="U40" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="V40" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="W40" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="X40" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y40" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="U40" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="V40" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="W40" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="X40" s="7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.15">
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -4432,7 +4612,7 @@
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -4458,7 +4638,7 @@
       <c r="W42" s="7"/>
       <c r="X42" s="7"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -4484,7 +4664,7 @@
       <c r="W43" s="7"/>
       <c r="X43" s="7"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -4510,7 +4690,7 @@
       <c r="W44" s="7"/>
       <c r="X44" s="7"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -4536,7 +4716,7 @@
       <c r="W45" s="7"/>
       <c r="X45" s="7"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -4562,7 +4742,7 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -4588,7 +4768,7 @@
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -4643,28 +4823,30 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="W16" r:id="rId1" xr:uid="{980A8705-7984-584F-AA67-D26C392ABC82}"/>
-    <hyperlink ref="W2" r:id="rId2" xr:uid="{9D626AFB-AED7-6E45-B753-789A1F6791C1}"/>
-    <hyperlink ref="W3" r:id="rId3" xr:uid="{C1F9917A-BBEE-3848-A846-5585A2FCCC16}"/>
-    <hyperlink ref="W4" r:id="rId4" xr:uid="{E61BB65B-5618-D842-B6B5-1D004A053D60}"/>
-    <hyperlink ref="W5" r:id="rId5" xr:uid="{030CB02F-3E38-AE45-AC1C-EE5651975CBA}"/>
-    <hyperlink ref="W6" r:id="rId6" xr:uid="{232A6A28-624D-CE40-BFCA-AD0E1FB7DF56}"/>
-    <hyperlink ref="W7" r:id="rId7" xr:uid="{C26CF64B-E057-8241-B386-6B0B94FD84CC}"/>
-    <hyperlink ref="W8" r:id="rId8" xr:uid="{FF6237C1-652C-1A4A-B04E-3FB26C32DBD5}"/>
-    <hyperlink ref="W9" r:id="rId9" xr:uid="{FE5C09BA-9D83-1C4D-A289-7D742AB36DC4}"/>
-    <hyperlink ref="W10" r:id="rId10" xr:uid="{28CFDF16-2940-5642-9869-C1E5F4C077CE}"/>
-    <hyperlink ref="W11" r:id="rId11" xr:uid="{C215718F-64A5-EA4F-8EA7-85C30B114214}"/>
-    <hyperlink ref="W12" r:id="rId12" xr:uid="{BE9CC28B-94CE-B24E-A74E-3D2ADB3217C6}"/>
-    <hyperlink ref="W13" r:id="rId13" xr:uid="{66457491-26B9-9F44-8331-CABFE31C9F72}"/>
-    <hyperlink ref="W14" r:id="rId14" xr:uid="{56EA8146-7375-2940-8CE7-621D3D82E155}"/>
-    <hyperlink ref="W15" r:id="rId15" xr:uid="{B991F48F-963A-5548-9E1D-97F06C683698}"/>
-    <hyperlink ref="W20" r:id="rId16" xr:uid="{AE74A4E6-305E-5F49-B0FE-9AAB97F6A3DF}"/>
-    <hyperlink ref="W40" r:id="rId17" xr:uid="{58E4C55D-2972-6044-88B9-E8D053273528}"/>
+    <hyperlink ref="X16" r:id="rId1" xr:uid="{06435D38-8656-894B-97C5-96B4F9A81B16}"/>
+    <hyperlink ref="X2" r:id="rId2" xr:uid="{EB14855D-0E7A-E441-A18B-4D016EB12E29}"/>
+    <hyperlink ref="X3" r:id="rId3" xr:uid="{C15DA009-4697-1244-8BAF-3240FF96A711}"/>
+    <hyperlink ref="X4" r:id="rId4" xr:uid="{5E45C078-1936-E646-A05B-0E269E699502}"/>
+    <hyperlink ref="X5" r:id="rId5" xr:uid="{3508BBD7-0686-214F-A732-F9D99867F37B}"/>
+    <hyperlink ref="X6" r:id="rId6" xr:uid="{44518A87-F14F-2046-B2D0-50BABBFE9F23}"/>
+    <hyperlink ref="X7" r:id="rId7" xr:uid="{9C71B0A9-7283-EE47-AD40-883AED7F6E3B}"/>
+    <hyperlink ref="X8" r:id="rId8" xr:uid="{A85AF766-CAB8-B745-B598-2A8703297230}"/>
+    <hyperlink ref="X9" r:id="rId9" xr:uid="{F4B0D80A-79B6-DA48-A301-0E18C15056FB}"/>
+    <hyperlink ref="X10" r:id="rId10" xr:uid="{3BA8B50E-BC9D-474A-B127-1A577C5A99E5}"/>
+    <hyperlink ref="X11" r:id="rId11" xr:uid="{D5D753E2-5C02-104F-8613-55614BC4ECCC}"/>
+    <hyperlink ref="X12" r:id="rId12" xr:uid="{F1B98F28-3440-4A4D-83F2-020B386BE961}"/>
+    <hyperlink ref="X13" r:id="rId13" xr:uid="{CEF4A8E3-B3D1-6D41-BC9D-129C9F04AB13}"/>
+    <hyperlink ref="X14" r:id="rId14" xr:uid="{7E56F984-036C-054B-AC54-65CDB8B27F35}"/>
+    <hyperlink ref="X15" r:id="rId15" xr:uid="{9464CCC8-2CFE-574E-A143-DA3F1F527DE6}"/>
+    <hyperlink ref="X20" r:id="rId16" xr:uid="{2FC3FD58-112F-F84B-9085-DE9B38C1019B}"/>
+    <hyperlink ref="X40" r:id="rId17" xr:uid="{DF8C6875-75B1-2349-8BCD-C0BD730420EB}"/>
+    <hyperlink ref="X39" r:id="rId18" xr:uid="{AC8170B0-D17B-354F-9989-7415944888AE}"/>
+    <hyperlink ref="X36" r:id="rId19" xr:uid="{CE12026F-61DF-C042-AA3B-3849F3B3051B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId18"/>
+  <legacyDrawing r:id="rId20"/>
   <tableParts count="1">
-    <tablePart r:id="rId19"/>
+    <tablePart r:id="rId21"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/rigi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B70C9F-C055-7A4F-93F9-A7FEFFAD449A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE43CF1-466E-8E47-B77C-8FF110ADE773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36440" yWindow="0" windowWidth="32360" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1049,7 +1049,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1124,12 +1124,6 @@
       <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2205,7 +2199,7 @@
         <v>287</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D4" s="8">
         <v>33</v>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/rigi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE43CF1-466E-8E47-B77C-8FF110ADE773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0085A19-ECED-6C4C-89CD-B1A7BE41161F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36440" yWindow="0" windowWidth="32360" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="940" yWindow="1160" windowWidth="32360" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <author>tc={EA61046C-C94E-C449-8761-ABD505A37332}</author>
     <author>tc={9E845984-16BC-D640-8568-DCBC39BD282B}</author>
     <author>tc={D756854B-3370-2C47-8E59-D458EBCA5109}</author>
-    <author>tc={909B81E5-AB38-BB4F-A77E-C63D2711848A}</author>
+    <author>tc={F654CC8D-FD5A-6343-8A74-B7DC43C44B1A}</author>
   </authors>
   <commentList>
     <comment ref="E1" authorId="0" shapeId="0" xr:uid="{CC7FC192-DD2F-524F-965B-B519233399BD}">
@@ -78,7 +78,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="N3" authorId="4" shapeId="0" xr:uid="{909B81E5-AB38-BB4F-A77E-C63D2711848A}">
+    <comment ref="N3" authorId="4" shapeId="0" xr:uid="{F654CC8D-FD5A-6343-8A74-B7DC43C44B1A}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="315">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -442,13 +442,7 @@
     <t>Sucursal Dedicada Midstream RDA</t>
   </si>
   <si>
-    <t>Sal de Oro</t>
-  </si>
-  <si>
     <t>Posco (Corea del Sur)</t>
-  </si>
-  <si>
-    <t>Argentina S.A. (Posco)</t>
   </si>
   <si>
     <t>Sal de Vida</t>
@@ -1041,6 +1035,30 @@
   <si>
     <t>Extracción, producción y exportación de cobre, oro y plata de los yacimientos Josemaría y Filo del Sol ubicados en la provincia de San Juan, República Argentina, así como la exploración de las concesiones mineras que forman parte del proyecto y el desarrollo de la infraestructura necesaria para su ejecución. Incluye infraestructura clave para operaciones de minería a cielo abierto: una planta concentradora para el procesamiento de minerales, instalaciones de lixiviación, infraestructura eléctrica, sistemas de suministro de agua, caminos de acceso y alojamientos.</t>
   </si>
+  <si>
+    <t>Sal de Oro II</t>
+  </si>
+  <si>
+    <t>Construcción de una planta destinada a la producción de carbonato de litio y su infraestructura complementaria. La planta tendrá una capacidad operativa aproximada de 23.000 toneladas anuales, que se obtendrá a través de un proceso convencional de evaporación solar y tratamiento químico de salmuera.</t>
+  </si>
+  <si>
+    <t>Posco Argentina SAU SDE</t>
+  </si>
+  <si>
+    <t>30-71922048-3</t>
+  </si>
+  <si>
+    <t>Res. 1157/2026</t>
+  </si>
+  <si>
+    <t>Signos fuertes de preexistencia del Proyecto Sal de Oro II. POSCO Holdings aprobó la inversión de la segunda fase en octubre de 2022; en junio de 2023, antes del primer anuncio del RIGI, el Gobierno nacional y la empresa comunicaron el inicio de construcción de una planta de carbonato de litio de 23.000 toneladas anuales; y en abril de 2024 POSCO obtuvo financiamiento por hasta USD 668 millones para esa misma fase. Las coincidencias de empresa, localización, producto, capacidad y etapa indican que se trata sustancialmente del mismo proyecto incorporado posteriormente al régimen.</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/345279/20260731</t>
+  </si>
+  <si>
+    <t>Res. 1157/2026; Globaris; MECON</t>
+  </si>
 </sst>
 </file>
 
@@ -1049,7 +1067,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1107,23 +1125,10 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF212529"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1189,7 +1194,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1225,19 +1230,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1247,7 +1240,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Notas" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="27">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1267,6 +1260,7 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
@@ -1293,7 +1287,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1554,7 +1548,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1641,20 +1635,6 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1722,7 +1702,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC5949B-99C1-C640-8DA2-C585B697BBE1}" name="ProyectosIntegrados2" displayName="ProyectosIntegrados2" ref="A1:Y40" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC5949B-99C1-C640-8DA2-C585B697BBE1}" name="ProyectosIntegrados2" displayName="ProyectosIntegrados2" ref="A1:Y40" headerRowDxfId="26" totalsRowDxfId="25">
   <tableColumns count="25">
     <tableColumn id="2" xr3:uid="{1FB8F74D-9682-B440-94D1-B6000493E00B}" name="VPU" dataDxfId="24"/>
     <tableColumn id="22" xr3:uid="{5F9EE6EB-2E4C-E743-B117-A1464438FFC7}" name="Descripción_del_proyecto" dataDxfId="23"/>
@@ -1747,7 +1727,7 @@
     <tableColumn id="15" xr3:uid="{AB9E3FD5-D9E1-FB4C-805E-4DC1E2E4F884}" name="norma_aprobacion" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{32A3F66C-F383-6A4F-BC9B-CE60E9775140}" name="Clasificacion_preexistencia_boletin_oficial" dataDxfId="3"/>
     <tableColumn id="23" xr3:uid="{8FFE7748-3D7D-F44F-9EE0-37998D10E3B7}" name="Justificacion_preexistencia_boletin_oficial" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{B5F0282B-C127-7C40-86CC-663CD39DAAF5}" name="link_norma" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{B5F0282B-C127-7C40-86CC-663CD39DAAF5}" name="link_norma" dataDxfId="1" dataCellStyle="Hipervínculo"/>
     <tableColumn id="20" xr3:uid="{4245686F-374C-B840-9963-4B9AF6D5BD62}" name="Fuentes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1945,7 +1925,7 @@
     <text xml:space="preserve">La fuente de datos de esta variable es el monitor del RIGI del MECON
 </text>
   </threadedComment>
-  <threadedComment ref="N3" dT="2026-06-09T13:10:11.61" personId="{2E8DF262-CB25-3049-80AF-0C6513AADFB8}" id="{909B81E5-AB38-BB4F-A77E-C63D2711848A}">
+  <threadedComment ref="N3" dT="2026-06-09T13:10:11.61" personId="{2E8DF262-CB25-3049-80AF-0C6513AADFB8}" id="{F654CC8D-FD5A-6343-8A74-B7DC43C44B1A}">
     <text xml:space="preserve">Que el solicitante declaró que el proyecto implicará una inversión total de entre dólares estadounidenses dos mil novecientos millones (USD 2.900.000.000) y dólares estadounidenses tres mil doscientos millones (USD 3.200.000.000). Se computa el promedio
 </text>
   </threadedComment>
@@ -1957,18 +1937,18 @@
   <dimension ref="A1:Y49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="94.33203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="94.33203125" style="16"/>
+    <col min="1" max="16384" width="94.33203125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1977,10 +1957,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>2</v>
@@ -1989,7 +1969,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>4</v>
@@ -1998,43 +1978,43 @@
         <v>5</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>148</v>
-      </c>
       <c r="Q1" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Y1" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.15">
@@ -2042,10 +2022,10 @@
         <v>40</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D2" s="8">
         <v>7</v>
@@ -2054,19 +2034,19 @@
         <v>41</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>42</v>
@@ -2102,27 +2082,27 @@
         <v>43</v>
       </c>
       <c r="V2" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D3" s="8">
         <v>13</v>
@@ -2134,16 +2114,16 @@
         <v>67</v>
       </c>
       <c r="G3" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>175</v>
-      </c>
       <c r="J3" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>42</v>
@@ -2179,27 +2159,27 @@
         <v>68</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="W3" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D4" s="8">
         <v>33</v>
@@ -2211,7 +2191,7 @@
         <v>76</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>19</v>
@@ -2220,7 +2200,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
@@ -2256,27 +2236,27 @@
         <v>77</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Y4" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D5" s="8">
         <v>10</v>
@@ -2288,7 +2268,7 @@
         <v>55</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>19</v>
@@ -2297,7 +2277,7 @@
         <v>56</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
@@ -2333,16 +2313,16 @@
         <v>57</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.15">
@@ -2350,10 +2330,10 @@
         <v>49</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D6" s="8">
         <v>9</v>
@@ -2365,7 +2345,7 @@
         <v>51</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>19</v>
@@ -2374,7 +2354,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>38</v>
@@ -2410,27 +2390,27 @@
         <v>53</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D7" s="8">
         <v>3</v>
@@ -2442,16 +2422,16 @@
         <v>24</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>25</v>
@@ -2487,27 +2467,27 @@
         <v>27</v>
       </c>
       <c r="V7" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="W7" s="13" t="s">
-        <v>233</v>
+        <v>180</v>
+      </c>
+      <c r="W7" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Y7" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
@@ -2519,22 +2499,22 @@
         <v>9</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M8" s="9">
         <v>550</v>
@@ -2564,27 +2544,27 @@
         <v>13</v>
       </c>
       <c r="V8" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>291</v>
+      <c r="B9" s="7" t="s">
+        <v>289</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D9" s="8">
         <v>2</v>
@@ -2595,20 +2575,20 @@
       <c r="F9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="14" t="s">
-        <v>199</v>
+      <c r="G9" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>179</v>
+        <v>187</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>21</v>
@@ -2641,27 +2621,27 @@
         <v>22</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="X9" s="15" t="s">
-        <v>159</v>
+        <v>233</v>
+      </c>
+      <c r="X9" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="75" x14ac:dyDescent="0.15">
-      <c r="A10" s="14" t="s">
-        <v>203</v>
+      <c r="A10" s="7" t="s">
+        <v>201</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D10" s="8">
         <v>14</v>
@@ -2670,19 +2650,19 @@
         <v>69</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>204</v>
+        <v>187</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -2717,17 +2697,17 @@
       <c r="U10" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="V10" s="14" t="s">
-        <v>169</v>
+      <c r="V10" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="X10" s="15" t="s">
-        <v>201</v>
+        <v>234</v>
+      </c>
+      <c r="X10" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="75" x14ac:dyDescent="0.15">
@@ -2735,10 +2715,10 @@
         <v>44</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D11" s="8">
         <v>8</v>
@@ -2750,7 +2730,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>47</v>
@@ -2759,7 +2739,7 @@
         <v>47</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>32</v>
@@ -2795,27 +2775,27 @@
         <v>48</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="X11" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="60" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D12" s="8">
         <v>12</v>
@@ -2827,7 +2807,7 @@
         <v>61</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>62</v>
@@ -2836,7 +2816,7 @@
         <v>63</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>64</v>
@@ -2872,16 +2852,16 @@
         <v>65</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="W12" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="Y12" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="120" x14ac:dyDescent="0.15">
@@ -2889,10 +2869,10 @@
         <v>28</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D13" s="8">
         <v>4</v>
@@ -2904,7 +2884,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>10</v>
@@ -2949,27 +2929,27 @@
         <v>34</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="120" x14ac:dyDescent="0.15">
-      <c r="A14" s="17" t="s">
-        <v>306</v>
+      <c r="A14" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D14" s="8">
         <v>11</v>
@@ -2978,10 +2958,10 @@
         <v>54</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>19</v>
@@ -2990,7 +2970,7 @@
         <v>56</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>58</v>
@@ -3026,16 +3006,16 @@
         <v>59</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W14" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="X14" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.15">
@@ -3043,10 +3023,10 @@
         <v>71</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D15" s="8">
         <v>39</v>
@@ -3058,7 +3038,7 @@
         <v>73</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>19</v>
@@ -3067,7 +3047,7 @@
         <v>56</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>58</v>
@@ -3103,16 +3083,16 @@
         <v>74</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="W15" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="X15" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y15" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="45" x14ac:dyDescent="0.15">
@@ -3120,10 +3100,10 @@
         <v>35</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D16" s="8">
         <v>5</v>
@@ -3135,13 +3115,13 @@
         <v>37</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
@@ -3178,16 +3158,16 @@
         <v>39</v>
       </c>
       <c r="V16" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="W16" s="13" t="s">
-        <v>242</v>
+        <v>180</v>
+      </c>
+      <c r="W16" s="7" t="s">
+        <v>240</v>
       </c>
       <c r="X16" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Y16" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="15" x14ac:dyDescent="0.15">
@@ -3227,7 +3207,7 @@
       </c>
       <c r="O17" s="9"/>
       <c r="P17" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q17" s="7"/>
       <c r="R17" s="10">
@@ -3240,14 +3220,14 @@
       <c r="W17" s="7"/>
       <c r="X17" s="12"/>
       <c r="Y17" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8">
         <v>16</v>
@@ -3258,14 +3238,14 @@
       <c r="F18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="14"/>
+      <c r="G18" s="7"/>
       <c r="H18" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="J18" s="14"/>
+      <c r="J18" s="7"/>
       <c r="K18" s="7" t="s">
         <v>85</v>
       </c>
@@ -3280,7 +3260,7 @@
       </c>
       <c r="O18" s="9"/>
       <c r="P18" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q18" s="7"/>
       <c r="R18" s="10">
@@ -3291,13 +3271,13 @@
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
-      <c r="X18" s="15"/>
+      <c r="X18" s="12"/>
       <c r="Y18" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="15" x14ac:dyDescent="0.15">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="7" t="s">
         <v>86</v>
       </c>
       <c r="B19" s="7"/>
@@ -3311,14 +3291,14 @@
       <c r="F19" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G19" s="14"/>
+      <c r="G19" s="7"/>
       <c r="H19" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J19" s="14"/>
+      <c r="J19" s="7"/>
       <c r="K19" s="7" t="s">
         <v>89</v>
       </c>
@@ -3333,7 +3313,7 @@
       </c>
       <c r="O19" s="9"/>
       <c r="P19" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q19" s="7"/>
       <c r="R19" s="10">
@@ -3344,20 +3324,20 @@
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
-      <c r="X19" s="15"/>
+      <c r="X19" s="12"/>
       <c r="Y19" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="45" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>225</v>
+        <v>217</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D20" s="8">
         <v>18</v>
@@ -3366,10 +3346,10 @@
         <v>90</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>220</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>19</v>
@@ -3377,8 +3357,8 @@
       <c r="I20" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J20" s="14" t="s">
-        <v>220</v>
+      <c r="J20" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>91</v>
@@ -3411,26 +3391,26 @@
         <v>46177</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="V20" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W20" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="X20" s="15" t="s">
-        <v>224</v>
+        <v>241</v>
+      </c>
+      <c r="X20" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="Y20" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="15" x14ac:dyDescent="0.15">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="14"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="8">
         <v>19</v>
@@ -3438,17 +3418,17 @@
       <c r="E21" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="14"/>
+      <c r="G21" s="7"/>
       <c r="H21" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="14"/>
+      <c r="J21" s="7"/>
       <c r="K21" s="7" t="s">
         <v>89</v>
       </c>
@@ -3463,7 +3443,7 @@
       </c>
       <c r="O21" s="9"/>
       <c r="P21" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q21" s="7"/>
       <c r="R21" s="10">
@@ -3474,9 +3454,9 @@
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
-      <c r="X21" s="15"/>
+      <c r="X21" s="12"/>
       <c r="Y21" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="15" x14ac:dyDescent="0.15">
@@ -3494,7 +3474,7 @@
       <c r="F22" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G22" s="14"/>
+      <c r="G22" s="7"/>
       <c r="H22" s="9" t="s">
         <v>19</v>
       </c>
@@ -3516,7 +3496,7 @@
       </c>
       <c r="O22" s="9"/>
       <c r="P22" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q22" s="7"/>
       <c r="R22" s="10">
@@ -3527,13 +3507,13 @@
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
-      <c r="X22" s="15"/>
+      <c r="X22" s="12"/>
       <c r="Y22" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="15" x14ac:dyDescent="0.15">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="7" t="s">
         <v>98</v>
       </c>
       <c r="B23" s="7"/>
@@ -3547,14 +3527,14 @@
       <c r="F23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="14"/>
+      <c r="G23" s="7"/>
       <c r="H23" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="14"/>
+      <c r="J23" s="7"/>
       <c r="K23" s="7" t="s">
         <v>89</v>
       </c>
@@ -3569,7 +3549,7 @@
       </c>
       <c r="O23" s="9"/>
       <c r="P23" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q23" s="7"/>
       <c r="R23" s="10">
@@ -3580,16 +3560,16 @@
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
       <c r="W23" s="7"/>
-      <c r="X23" s="15"/>
+      <c r="X23" s="12"/>
       <c r="Y23" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B24" s="14"/>
+        <v>134</v>
+      </c>
+      <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="8">
         <v>37</v>
@@ -3598,16 +3578,16 @@
         <v>114</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G24" s="14"/>
+        <v>135</v>
+      </c>
+      <c r="G24" s="7"/>
       <c r="H24" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J24" s="14"/>
+      <c r="J24" s="7"/>
       <c r="K24" s="7" t="s">
         <v>32</v>
       </c>
@@ -3622,7 +3602,7 @@
       </c>
       <c r="O24" s="9"/>
       <c r="P24" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q24" s="7"/>
       <c r="R24" s="10">
@@ -3633,44 +3613,44 @@
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
       <c r="W24" s="7"/>
-      <c r="X24" s="15"/>
+      <c r="X24" s="12"/>
       <c r="Y24" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="90" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D25" s="8">
         <v>38</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>12</v>
@@ -3700,24 +3680,24 @@
         <v>46198</v>
       </c>
       <c r="U25" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="V25" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="W25" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="X25" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y25" s="7" t="s">
         <v>266</v>
-      </c>
-      <c r="V25" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="W25" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="X25" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="Y25" s="7" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -3725,10 +3705,10 @@
         <v>40</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="9" t="s">
@@ -3752,7 +3732,7 @@
       </c>
       <c r="O26" s="9"/>
       <c r="P26" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q26" s="7"/>
       <c r="R26" s="10">
@@ -3765,12 +3745,12 @@
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -3778,7 +3758,7 @@
         <v>41</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>14</v>
@@ -3805,7 +3785,7 @@
       </c>
       <c r="O27" s="9"/>
       <c r="P27" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q27" s="7"/>
       <c r="R27" s="10">
@@ -3818,12 +3798,12 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -3831,7 +3811,7 @@
         <v>32</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>14</v>
@@ -3858,7 +3838,7 @@
       </c>
       <c r="O28" s="9"/>
       <c r="P28" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q28" s="7"/>
       <c r="R28" s="10">
@@ -3871,32 +3851,32 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="15" x14ac:dyDescent="0.15">
-      <c r="A29" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="14"/>
+      <c r="A29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="8">
         <v>34</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="G29" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="7"/>
       <c r="H29" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J29" s="14"/>
+      <c r="J29" s="7"/>
       <c r="K29" s="7" t="s">
         <v>20</v>
       </c>
@@ -3911,7 +3891,7 @@
       </c>
       <c r="O29" s="9"/>
       <c r="P29" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q29" s="7"/>
       <c r="R29" s="10">
@@ -3924,12 +3904,12 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
       <c r="Y29" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -3937,10 +3917,10 @@
         <v>35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="9" t="s">
@@ -3964,7 +3944,7 @@
       </c>
       <c r="O30" s="9"/>
       <c r="P30" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q30" s="7"/>
       <c r="R30" s="10">
@@ -3977,12 +3957,12 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -3993,7 +3973,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="9" t="s">
@@ -4017,7 +3997,7 @@
       </c>
       <c r="O31" s="9"/>
       <c r="P31" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q31" s="7"/>
       <c r="R31" s="10">
@@ -4030,7 +4010,7 @@
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
       <c r="Y31" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="15" x14ac:dyDescent="0.15">
@@ -4070,7 +4050,7 @@
       </c>
       <c r="O32" s="9"/>
       <c r="P32" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q32" s="7"/>
       <c r="R32" s="10" t="s">
@@ -4083,7 +4063,7 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
       <c r="Y32" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="15" x14ac:dyDescent="0.15">
@@ -4123,7 +4103,7 @@
       </c>
       <c r="O33" s="9"/>
       <c r="P33" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q33" s="7"/>
       <c r="R33" s="10">
@@ -4136,7 +4116,7 @@
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:25" ht="15" x14ac:dyDescent="0.15">
@@ -4176,7 +4156,7 @@
       </c>
       <c r="O34" s="9"/>
       <c r="P34" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q34" s="7"/>
       <c r="R34" s="10">
@@ -4189,7 +4169,7 @@
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
       <c r="Y34" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:25" ht="15" x14ac:dyDescent="0.15">
@@ -4229,7 +4209,7 @@
       </c>
       <c r="O35" s="9"/>
       <c r="P35" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q35" s="7"/>
       <c r="R35" s="10">
@@ -4242,18 +4222,18 @@
       <c r="W35" s="7"/>
       <c r="X35" s="7"/>
       <c r="Y35" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="90" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>275</v>
+        <v>268</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>273</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D36" s="8">
         <v>26</v>
@@ -4264,17 +4244,17 @@
       <c r="F36" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="G36" s="17" t="s">
-        <v>274</v>
+      <c r="G36" s="7" t="s">
+        <v>272</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>273</v>
+        <v>163</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>89</v>
@@ -4307,77 +4287,101 @@
         <v>46224</v>
       </c>
       <c r="U36" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="V36" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="W36" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="X36" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="Y36" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="90" x14ac:dyDescent="0.15">
+      <c r="A37" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="V36" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="W36" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="X36" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y36" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" ht="15" x14ac:dyDescent="0.15">
-      <c r="A37" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
+      <c r="B37" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>180</v>
+      </c>
       <c r="D37" s="8">
         <v>27</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="G37" s="7"/>
+        <v>309</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>310</v>
+      </c>
       <c r="H37" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J37" s="7"/>
+      <c r="J37" s="7" t="s">
+        <v>184</v>
+      </c>
       <c r="K37" s="7" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="L37" s="7" t="s">
         <v>21</v>
       </c>
       <c r="M37" s="9">
-        <v>845</v>
+        <v>547</v>
       </c>
       <c r="N37" s="9">
-        <v>845</v>
-      </c>
-      <c r="O37" s="9"/>
+        <v>547</v>
+      </c>
+      <c r="O37" s="9">
+        <v>207.9364272</v>
+      </c>
       <c r="P37" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q37" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="Q37" s="7">
+        <v>2335</v>
+      </c>
       <c r="R37" s="10">
         <v>45595</v>
       </c>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="7"/>
+      <c r="S37" s="10">
+        <v>46185</v>
+      </c>
+      <c r="T37" s="10">
+        <v>46234</v>
+      </c>
+      <c r="U37" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="V37" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="W37" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="X37" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="Y37" s="7" t="s">
-        <v>226</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -4388,7 +4392,7 @@
         <v>54</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="9" t="s">
@@ -4412,7 +4416,7 @@
       </c>
       <c r="O38" s="9"/>
       <c r="P38" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="7"/>
       <c r="R38" s="10">
@@ -4425,28 +4429,28 @@
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:25" ht="90" x14ac:dyDescent="0.15">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>282</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>284</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="8">
         <v>29</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>281</v>
+        <v>120</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>279</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>19</v>
@@ -4455,7 +4459,7 @@
         <v>56</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>58</v>
@@ -4488,51 +4492,51 @@
         <v>46232</v>
       </c>
       <c r="U39" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="V39" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="W39" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="X39" s="15" t="s">
-        <v>279</v>
+        <v>167</v>
+      </c>
+      <c r="W39" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="X39" s="12" t="s">
+        <v>277</v>
       </c>
       <c r="Y39" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="90" x14ac:dyDescent="0.15">
-      <c r="A40" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>308</v>
+      <c r="A40" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D40" s="8">
         <v>31</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>299</v>
+        <v>123</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>297</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>179</v>
+        <v>298</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>25</v>
@@ -4565,19 +4569,19 @@
         <v>46233</v>
       </c>
       <c r="U40" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="V40" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="W40" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="X40" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y40" s="7" t="s">
         <v>301</v>
-      </c>
-      <c r="V40" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="W40" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="X40" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="Y40" s="7" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.15">
@@ -4817,25 +4821,25 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="X16" r:id="rId1" xr:uid="{06435D38-8656-894B-97C5-96B4F9A81B16}"/>
-    <hyperlink ref="X2" r:id="rId2" xr:uid="{EB14855D-0E7A-E441-A18B-4D016EB12E29}"/>
-    <hyperlink ref="X3" r:id="rId3" xr:uid="{C15DA009-4697-1244-8BAF-3240FF96A711}"/>
-    <hyperlink ref="X4" r:id="rId4" xr:uid="{5E45C078-1936-E646-A05B-0E269E699502}"/>
-    <hyperlink ref="X5" r:id="rId5" xr:uid="{3508BBD7-0686-214F-A732-F9D99867F37B}"/>
-    <hyperlink ref="X6" r:id="rId6" xr:uid="{44518A87-F14F-2046-B2D0-50BABBFE9F23}"/>
-    <hyperlink ref="X7" r:id="rId7" xr:uid="{9C71B0A9-7283-EE47-AD40-883AED7F6E3B}"/>
-    <hyperlink ref="X8" r:id="rId8" xr:uid="{A85AF766-CAB8-B745-B598-2A8703297230}"/>
-    <hyperlink ref="X9" r:id="rId9" xr:uid="{F4B0D80A-79B6-DA48-A301-0E18C15056FB}"/>
-    <hyperlink ref="X10" r:id="rId10" xr:uid="{3BA8B50E-BC9D-474A-B127-1A577C5A99E5}"/>
-    <hyperlink ref="X11" r:id="rId11" xr:uid="{D5D753E2-5C02-104F-8613-55614BC4ECCC}"/>
-    <hyperlink ref="X12" r:id="rId12" xr:uid="{F1B98F28-3440-4A4D-83F2-020B386BE961}"/>
-    <hyperlink ref="X13" r:id="rId13" xr:uid="{CEF4A8E3-B3D1-6D41-BC9D-129C9F04AB13}"/>
-    <hyperlink ref="X14" r:id="rId14" xr:uid="{7E56F984-036C-054B-AC54-65CDB8B27F35}"/>
-    <hyperlink ref="X15" r:id="rId15" xr:uid="{9464CCC8-2CFE-574E-A143-DA3F1F527DE6}"/>
-    <hyperlink ref="X20" r:id="rId16" xr:uid="{2FC3FD58-112F-F84B-9085-DE9B38C1019B}"/>
-    <hyperlink ref="X40" r:id="rId17" xr:uid="{DF8C6875-75B1-2349-8BCD-C0BD730420EB}"/>
-    <hyperlink ref="X39" r:id="rId18" xr:uid="{AC8170B0-D17B-354F-9989-7415944888AE}"/>
-    <hyperlink ref="X36" r:id="rId19" xr:uid="{CE12026F-61DF-C042-AA3B-3849F3B3051B}"/>
+    <hyperlink ref="X16" r:id="rId1" xr:uid="{D2412230-C3CD-7141-A25E-81BAF21A6174}"/>
+    <hyperlink ref="X2" r:id="rId2" xr:uid="{6D3504F9-33D3-5C42-ADC4-1F1B36F66242}"/>
+    <hyperlink ref="X3" r:id="rId3" xr:uid="{46673F91-F8F5-E946-A08B-B67632A08D9A}"/>
+    <hyperlink ref="X4" r:id="rId4" xr:uid="{68D4EB52-1EA3-C340-8AD8-D38DE0C9F22E}"/>
+    <hyperlink ref="X5" r:id="rId5" xr:uid="{012259F1-B4A3-1045-9E7A-AA126AE86681}"/>
+    <hyperlink ref="X6" r:id="rId6" xr:uid="{2C8B22AB-5777-4540-9E80-66B0C685703B}"/>
+    <hyperlink ref="X7" r:id="rId7" xr:uid="{49A07586-1F8E-8B41-AEA7-4C3E0536DD20}"/>
+    <hyperlink ref="X8" r:id="rId8" xr:uid="{56C3B5AD-00FB-E64B-9608-926539AA5FD6}"/>
+    <hyperlink ref="X9" r:id="rId9" xr:uid="{55AFF93D-C6FF-614A-B18E-808BD1FB3040}"/>
+    <hyperlink ref="X10" r:id="rId10" xr:uid="{4C306BC4-9928-3645-BF72-CEF21D95B062}"/>
+    <hyperlink ref="X11" r:id="rId11" xr:uid="{E51E5B00-AE31-004C-80CA-1046BF32CCCF}"/>
+    <hyperlink ref="X12" r:id="rId12" xr:uid="{10235633-5E5E-DD47-9890-13CA8ADBFF10}"/>
+    <hyperlink ref="X13" r:id="rId13" xr:uid="{C5CA1D0E-3350-CC43-8953-1CB241BB051B}"/>
+    <hyperlink ref="X14" r:id="rId14" xr:uid="{51CBFD06-0CB5-2C42-8727-D4B9CB369184}"/>
+    <hyperlink ref="X15" r:id="rId15" xr:uid="{8F2DFA35-F36C-F944-9C1B-42BE62E36FAC}"/>
+    <hyperlink ref="X20" r:id="rId16" xr:uid="{6349A6AC-03EB-6D4A-8F5A-A51D3A9078D4}"/>
+    <hyperlink ref="X40" r:id="rId17" xr:uid="{32F573A4-ED90-7044-AEEE-F5401A638E68}"/>
+    <hyperlink ref="X39" r:id="rId18" xr:uid="{18E22821-D2A5-A440-B5C5-EDB3995DD45E}"/>
+    <hyperlink ref="X36" r:id="rId19" xr:uid="{027F49BC-6705-E14A-ACC3-B787972340B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId20"/>
@@ -4855,7 +4859,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
